--- a/input/BOM.xlsx
+++ b/input/BOM.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="5">
     <font>
       <name val="Tahoma"/>
       <sz val="10"/>
@@ -34,18 +34,6 @@
       <name val="Tahoma"/>
       <family val="2"/>
       <color theme="10"/>
-      <sz val="10"/>
-      <u val="single"/>
-    </font>
-    <font>
-      <name val="Tahoma"/>
-      <color rgb="FF0563C1"/>
-      <sz val="10"/>
-      <u val="single"/>
-    </font>
-    <font>
-      <name val="Tahoma"/>
-      <color rgb="FF0563C1"/>
       <sz val="10"/>
       <u val="single"/>
     </font>
@@ -95,7 +83,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -164,6 +152,34 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0"/>
@@ -186,25 +202,25 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="1" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -606,19 +622,20 @@
   <dimension ref="A1:O535"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.88671875" defaultRowHeight="13.2"/>
   <cols>
-    <col width="25.5546875" customWidth="1" style="17" min="1" max="1"/>
-    <col width="9.33203125" bestFit="1" customWidth="1" style="17" min="2" max="2"/>
-    <col width="6.33203125" bestFit="1" customWidth="1" style="17" min="3" max="3"/>
-    <col width="15.5546875" bestFit="1" customWidth="1" style="17" min="4" max="4"/>
-    <col width="8" bestFit="1" customWidth="1" style="17" min="5" max="5"/>
-    <col width="10" bestFit="1" customWidth="1" style="17" min="6" max="6"/>
-    <col width="31.6640625" bestFit="1" customWidth="1" style="17" min="7" max="7"/>
-    <col width="26.6640625" bestFit="1" customWidth="1" style="17" min="8" max="9"/>
-    <col width="44.6640625" bestFit="1" customWidth="1" style="17" min="10" max="10"/>
-    <col width="7" bestFit="1" customWidth="1" style="17" min="11" max="11"/>
+    <col width="25.5546875" customWidth="1" style="20" min="1" max="1"/>
+    <col width="9.33203125" bestFit="1" customWidth="1" style="20" min="2" max="2"/>
+    <col width="6.33203125" bestFit="1" customWidth="1" style="20" min="3" max="3"/>
+    <col width="15.5546875" bestFit="1" customWidth="1" style="20" min="4" max="4"/>
+    <col width="8" bestFit="1" customWidth="1" style="20" min="5" max="5"/>
+    <col width="10" bestFit="1" customWidth="1" style="20" min="6" max="6"/>
+    <col width="31.6640625" bestFit="1" customWidth="1" style="20" min="7" max="7"/>
+    <col width="26.6640625" bestFit="1" customWidth="1" style="20" min="8" max="9"/>
+    <col width="44.6640625" bestFit="1" customWidth="1" style="20" min="10" max="10"/>
+    <col width="7" bestFit="1" customWidth="1" style="20" min="11" max="11"/>
     <col width="25.6640625" customWidth="1" style="6" min="12" max="12"/>
-    <col width="26.109375" bestFit="1" customWidth="1" style="17" min="13" max="13"/>
-    <col width="29.21875" customWidth="1" style="17" min="14" max="14"/>
+    <col width="26.109375" bestFit="1" customWidth="1" style="20" min="13" max="13"/>
+    <col width="29.33203125" customWidth="1" style="20" min="14" max="14"/>
+    <col width="19.109375" customWidth="1" style="20" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -647,7 +664,7 @@
           <t>Quantity</t>
         </is>
       </c>
-      <c r="F1" s="16" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Designator</t>
         </is>
@@ -677,24 +694,24 @@
           <t>Layer</t>
         </is>
       </c>
-      <c r="L1" s="13" t="inlineStr">
+      <c r="L1" s="11" t="inlineStr">
         <is>
           <t>Purchase Remarks</t>
         </is>
       </c>
-      <c r="M1" s="15" t="inlineStr">
+      <c r="M1" s="12" t="inlineStr">
         <is>
           <t>R&amp;D Remarks</t>
         </is>
       </c>
-      <c r="N1" s="15" t="inlineStr">
-        <is>
-          <t>Alternative</t>
-        </is>
-      </c>
-      <c r="O1" s="0" t="inlineStr">
-        <is>
-          <t>Jira Ticket</t>
+      <c r="N1" s="16" t="inlineStr">
+        <is>
+          <t>Alternative MPN</t>
+        </is>
+      </c>
+      <c r="O1" s="14" t="inlineStr">
+        <is>
+          <t>Alternative MANUF</t>
         </is>
       </c>
     </row>
@@ -750,7 +767,8 @@
       </c>
       <c r="L2" s="7" t="n"/>
       <c r="M2" s="8" t="n"/>
-      <c r="N2" s="8" t="n"/>
+      <c r="N2" s="17" t="n"/>
+      <c r="O2" s="15" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -804,7 +822,8 @@
       </c>
       <c r="L3" s="7" t="n"/>
       <c r="M3" s="8" t="n"/>
-      <c r="N3" s="8" t="n"/>
+      <c r="N3" s="17" t="n"/>
+      <c r="O3" s="15" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -858,7 +877,8 @@
       </c>
       <c r="L4" s="7" t="n"/>
       <c r="M4" s="8" t="n"/>
-      <c r="N4" s="8" t="n"/>
+      <c r="N4" s="17" t="n"/>
+      <c r="O4" s="15" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -900,7 +920,8 @@
       </c>
       <c r="L5" s="7" t="n"/>
       <c r="M5" s="8" t="n"/>
-      <c r="N5" s="8" t="n"/>
+      <c r="N5" s="17" t="n"/>
+      <c r="O5" s="15" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -942,7 +963,8 @@
       </c>
       <c r="L6" s="7" t="n"/>
       <c r="M6" s="8" t="n"/>
-      <c r="N6" s="8" t="n"/>
+      <c r="N6" s="17" t="n"/>
+      <c r="O6" s="15" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -984,7 +1006,8 @@
       </c>
       <c r="L7" s="7" t="n"/>
       <c r="M7" s="8" t="n"/>
-      <c r="N7" s="8" t="n"/>
+      <c r="N7" s="17" t="n"/>
+      <c r="O7" s="15" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -1026,7 +1049,8 @@
       </c>
       <c r="L8" s="7" t="n"/>
       <c r="M8" s="8" t="n"/>
-      <c r="N8" s="8" t="n"/>
+      <c r="N8" s="17" t="n"/>
+      <c r="O8" s="15" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -1080,7 +1104,8 @@
       </c>
       <c r="L9" s="7" t="n"/>
       <c r="M9" s="8" t="n"/>
-      <c r="N9" s="8" t="n"/>
+      <c r="N9" s="17" t="n"/>
+      <c r="O9" s="15" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -1122,7 +1147,8 @@
       </c>
       <c r="L10" s="7" t="n"/>
       <c r="M10" s="8" t="n"/>
-      <c r="N10" s="8" t="n"/>
+      <c r="N10" s="17" t="n"/>
+      <c r="O10" s="15" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1164,7 +1190,8 @@
       </c>
       <c r="L11" s="7" t="n"/>
       <c r="M11" s="8" t="n"/>
-      <c r="N11" s="8" t="n"/>
+      <c r="N11" s="17" t="n"/>
+      <c r="O11" s="15" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1218,7 +1245,8 @@
       </c>
       <c r="L12" s="7" t="n"/>
       <c r="M12" s="8" t="n"/>
-      <c r="N12" s="8" t="n"/>
+      <c r="N12" s="17" t="n"/>
+      <c r="O12" s="15" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -1260,7 +1288,8 @@
       </c>
       <c r="L13" s="7" t="n"/>
       <c r="M13" s="8" t="n"/>
-      <c r="N13" s="8" t="n"/>
+      <c r="N13" s="17" t="n"/>
+      <c r="O13" s="15" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -1302,7 +1331,8 @@
       </c>
       <c r="L14" s="7" t="n"/>
       <c r="M14" s="8" t="n"/>
-      <c r="N14" s="8" t="n"/>
+      <c r="N14" s="17" t="n"/>
+      <c r="O14" s="15" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -1344,7 +1374,8 @@
       </c>
       <c r="L15" s="7" t="n"/>
       <c r="M15" s="8" t="n"/>
-      <c r="N15" s="8" t="n"/>
+      <c r="N15" s="17" t="n"/>
+      <c r="O15" s="15" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -1386,7 +1417,8 @@
       </c>
       <c r="L16" s="7" t="n"/>
       <c r="M16" s="8" t="n"/>
-      <c r="N16" s="8" t="n"/>
+      <c r="N16" s="17" t="n"/>
+      <c r="O16" s="15" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -1428,7 +1460,8 @@
       </c>
       <c r="L17" s="7" t="n"/>
       <c r="M17" s="8" t="n"/>
-      <c r="N17" s="8" t="n"/>
+      <c r="N17" s="17" t="n"/>
+      <c r="O17" s="15" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -1482,7 +1515,8 @@
       </c>
       <c r="L18" s="7" t="n"/>
       <c r="M18" s="8" t="n"/>
-      <c r="N18" s="8" t="n"/>
+      <c r="N18" s="17" t="n"/>
+      <c r="O18" s="15" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -1536,7 +1570,8 @@
       </c>
       <c r="L19" s="7" t="n"/>
       <c r="M19" s="8" t="n"/>
-      <c r="N19" s="8" t="n"/>
+      <c r="N19" s="17" t="n"/>
+      <c r="O19" s="15" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -1590,7 +1625,8 @@
       </c>
       <c r="L20" s="7" t="n"/>
       <c r="M20" s="8" t="n"/>
-      <c r="N20" s="8" t="n"/>
+      <c r="N20" s="17" t="n"/>
+      <c r="O20" s="15" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -1632,7 +1668,8 @@
       </c>
       <c r="L21" s="7" t="n"/>
       <c r="M21" s="8" t="n"/>
-      <c r="N21" s="8" t="n"/>
+      <c r="N21" s="17" t="n"/>
+      <c r="O21" s="15" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -1674,7 +1711,8 @@
       </c>
       <c r="L22" s="7" t="n"/>
       <c r="M22" s="8" t="n"/>
-      <c r="N22" s="8" t="n"/>
+      <c r="N22" s="17" t="n"/>
+      <c r="O22" s="15" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -1716,7 +1754,8 @@
       </c>
       <c r="L23" s="7" t="n"/>
       <c r="M23" s="8" t="n"/>
-      <c r="N23" s="8" t="n"/>
+      <c r="N23" s="17" t="n"/>
+      <c r="O23" s="15" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -1758,7 +1797,8 @@
       </c>
       <c r="L24" s="7" t="n"/>
       <c r="M24" s="8" t="n"/>
-      <c r="N24" s="8" t="n"/>
+      <c r="N24" s="17" t="n"/>
+      <c r="O24" s="15" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -1800,7 +1840,8 @@
       </c>
       <c r="L25" s="7" t="n"/>
       <c r="M25" s="8" t="n"/>
-      <c r="N25" s="8" t="n"/>
+      <c r="N25" s="17" t="n"/>
+      <c r="O25" s="15" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -1854,7 +1895,8 @@
       </c>
       <c r="L26" s="7" t="n"/>
       <c r="M26" s="8" t="n"/>
-      <c r="N26" s="8" t="n"/>
+      <c r="N26" s="17" t="n"/>
+      <c r="O26" s="15" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -1896,7 +1938,8 @@
       </c>
       <c r="L27" s="7" t="n"/>
       <c r="M27" s="8" t="n"/>
-      <c r="N27" s="8" t="n"/>
+      <c r="N27" s="17" t="n"/>
+      <c r="O27" s="15" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -1950,7 +1993,8 @@
       </c>
       <c r="L28" s="7" t="n"/>
       <c r="M28" s="8" t="n"/>
-      <c r="N28" s="8" t="n"/>
+      <c r="N28" s="17" t="n"/>
+      <c r="O28" s="15" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -2004,7 +2048,8 @@
       </c>
       <c r="L29" s="7" t="n"/>
       <c r="M29" s="8" t="n"/>
-      <c r="N29" s="8" t="n"/>
+      <c r="N29" s="17" t="n"/>
+      <c r="O29" s="15" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
@@ -2058,7 +2103,8 @@
       </c>
       <c r="L30" s="7" t="n"/>
       <c r="M30" s="8" t="n"/>
-      <c r="N30" s="8" t="n"/>
+      <c r="N30" s="17" t="n"/>
+      <c r="O30" s="15" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -2100,7 +2146,8 @@
       </c>
       <c r="L31" s="7" t="n"/>
       <c r="M31" s="8" t="n"/>
-      <c r="N31" s="8" t="n"/>
+      <c r="N31" s="17" t="n"/>
+      <c r="O31" s="15" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -2142,7 +2189,8 @@
       </c>
       <c r="L32" s="7" t="n"/>
       <c r="M32" s="8" t="n"/>
-      <c r="N32" s="8" t="n"/>
+      <c r="N32" s="17" t="n"/>
+      <c r="O32" s="15" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -2184,7 +2232,8 @@
       </c>
       <c r="L33" s="7" t="n"/>
       <c r="M33" s="8" t="n"/>
-      <c r="N33" s="8" t="n"/>
+      <c r="N33" s="17" t="n"/>
+      <c r="O33" s="15" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
@@ -2226,7 +2275,8 @@
       </c>
       <c r="L34" s="7" t="n"/>
       <c r="M34" s="8" t="n"/>
-      <c r="N34" s="8" t="n"/>
+      <c r="N34" s="17" t="n"/>
+      <c r="O34" s="15" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -2268,7 +2318,8 @@
       </c>
       <c r="L35" s="7" t="n"/>
       <c r="M35" s="8" t="n"/>
-      <c r="N35" s="8" t="n"/>
+      <c r="N35" s="17" t="n"/>
+      <c r="O35" s="15" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
@@ -2322,7 +2373,8 @@
       </c>
       <c r="L36" s="7" t="n"/>
       <c r="M36" s="8" t="n"/>
-      <c r="N36" s="8" t="n"/>
+      <c r="N36" s="17" t="n"/>
+      <c r="O36" s="15" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -2376,7 +2428,8 @@
       </c>
       <c r="L37" s="7" t="n"/>
       <c r="M37" s="8" t="n"/>
-      <c r="N37" s="8" t="n"/>
+      <c r="N37" s="17" t="n"/>
+      <c r="O37" s="15" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -2418,7 +2471,8 @@
       </c>
       <c r="L38" s="7" t="n"/>
       <c r="M38" s="8" t="n"/>
-      <c r="N38" s="8" t="n"/>
+      <c r="N38" s="17" t="n"/>
+      <c r="O38" s="15" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -2460,7 +2514,8 @@
       </c>
       <c r="L39" s="7" t="n"/>
       <c r="M39" s="8" t="n"/>
-      <c r="N39" s="8" t="n"/>
+      <c r="N39" s="17" t="n"/>
+      <c r="O39" s="15" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -2514,7 +2569,8 @@
       </c>
       <c r="L40" s="7" t="n"/>
       <c r="M40" s="8" t="n"/>
-      <c r="N40" s="8" t="n"/>
+      <c r="N40" s="17" t="n"/>
+      <c r="O40" s="15" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -2556,7 +2612,8 @@
       </c>
       <c r="L41" s="7" t="n"/>
       <c r="M41" s="8" t="n"/>
-      <c r="N41" s="8" t="n"/>
+      <c r="N41" s="17" t="n"/>
+      <c r="O41" s="15" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
@@ -2598,7 +2655,8 @@
       </c>
       <c r="L42" s="7" t="n"/>
       <c r="M42" s="8" t="n"/>
-      <c r="N42" s="8" t="n"/>
+      <c r="N42" s="17" t="n"/>
+      <c r="O42" s="15" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
@@ -2640,7 +2698,8 @@
       </c>
       <c r="L43" s="7" t="n"/>
       <c r="M43" s="8" t="n"/>
-      <c r="N43" s="8" t="n"/>
+      <c r="N43" s="17" t="n"/>
+      <c r="O43" s="15" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -2682,7 +2741,8 @@
       </c>
       <c r="L44" s="7" t="n"/>
       <c r="M44" s="8" t="n"/>
-      <c r="N44" s="8" t="n"/>
+      <c r="N44" s="17" t="n"/>
+      <c r="O44" s="15" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -2736,7 +2796,8 @@
       </c>
       <c r="L45" s="7" t="n"/>
       <c r="M45" s="8" t="n"/>
-      <c r="N45" s="8" t="n"/>
+      <c r="N45" s="17" t="n"/>
+      <c r="O45" s="15" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
@@ -2778,7 +2839,8 @@
       </c>
       <c r="L46" s="7" t="n"/>
       <c r="M46" s="8" t="n"/>
-      <c r="N46" s="8" t="n"/>
+      <c r="N46" s="17" t="n"/>
+      <c r="O46" s="15" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -2820,7 +2882,8 @@
       </c>
       <c r="L47" s="7" t="n"/>
       <c r="M47" s="8" t="n"/>
-      <c r="N47" s="8" t="n"/>
+      <c r="N47" s="17" t="n"/>
+      <c r="O47" s="15" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
@@ -2874,7 +2937,8 @@
       </c>
       <c r="L48" s="7" t="n"/>
       <c r="M48" s="8" t="n"/>
-      <c r="N48" s="8" t="n"/>
+      <c r="N48" s="17" t="n"/>
+      <c r="O48" s="15" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
@@ -2928,7 +2992,8 @@
       </c>
       <c r="L49" s="7" t="n"/>
       <c r="M49" s="8" t="n"/>
-      <c r="N49" s="8" t="n"/>
+      <c r="N49" s="17" t="n"/>
+      <c r="O49" s="15" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
@@ -2970,7 +3035,8 @@
       </c>
       <c r="L50" s="7" t="n"/>
       <c r="M50" s="8" t="n"/>
-      <c r="N50" s="8" t="n"/>
+      <c r="N50" s="17" t="n"/>
+      <c r="O50" s="15" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
@@ -3024,7 +3090,8 @@
       </c>
       <c r="L51" s="7" t="n"/>
       <c r="M51" s="8" t="n"/>
-      <c r="N51" s="8" t="n"/>
+      <c r="N51" s="17" t="n"/>
+      <c r="O51" s="15" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
@@ -3066,7 +3133,8 @@
       </c>
       <c r="L52" s="7" t="n"/>
       <c r="M52" s="8" t="n"/>
-      <c r="N52" s="8" t="n"/>
+      <c r="N52" s="17" t="n"/>
+      <c r="O52" s="15" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
@@ -3120,7 +3188,8 @@
       </c>
       <c r="L53" s="7" t="n"/>
       <c r="M53" s="8" t="n"/>
-      <c r="N53" s="8" t="n"/>
+      <c r="N53" s="17" t="n"/>
+      <c r="O53" s="15" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
@@ -3174,7 +3243,8 @@
       </c>
       <c r="L54" s="7" t="n"/>
       <c r="M54" s="8" t="n"/>
-      <c r="N54" s="8" t="n"/>
+      <c r="N54" s="17" t="n"/>
+      <c r="O54" s="15" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
@@ -3228,7 +3298,8 @@
       </c>
       <c r="L55" s="7" t="n"/>
       <c r="M55" s="8" t="n"/>
-      <c r="N55" s="8" t="n"/>
+      <c r="N55" s="17" t="n"/>
+      <c r="O55" s="15" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
@@ -3282,7 +3353,8 @@
       </c>
       <c r="L56" s="7" t="n"/>
       <c r="M56" s="8" t="n"/>
-      <c r="N56" s="8" t="n"/>
+      <c r="N56" s="17" t="n"/>
+      <c r="O56" s="15" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
@@ -3336,7 +3408,8 @@
       </c>
       <c r="L57" s="7" t="n"/>
       <c r="M57" s="8" t="n"/>
-      <c r="N57" s="8" t="n"/>
+      <c r="N57" s="17" t="n"/>
+      <c r="O57" s="15" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
@@ -3378,7 +3451,8 @@
       </c>
       <c r="L58" s="7" t="n"/>
       <c r="M58" s="8" t="n"/>
-      <c r="N58" s="8" t="n"/>
+      <c r="N58" s="17" t="n"/>
+      <c r="O58" s="15" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
@@ -3420,7 +3494,8 @@
       </c>
       <c r="L59" s="7" t="n"/>
       <c r="M59" s="8" t="n"/>
-      <c r="N59" s="8" t="n"/>
+      <c r="N59" s="17" t="n"/>
+      <c r="O59" s="15" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
@@ -3474,7 +3549,8 @@
       </c>
       <c r="L60" s="7" t="n"/>
       <c r="M60" s="8" t="n"/>
-      <c r="N60" s="8" t="n"/>
+      <c r="N60" s="17" t="n"/>
+      <c r="O60" s="15" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
@@ -3516,7 +3592,8 @@
       </c>
       <c r="L61" s="7" t="n"/>
       <c r="M61" s="8" t="n"/>
-      <c r="N61" s="8" t="n"/>
+      <c r="N61" s="17" t="n"/>
+      <c r="O61" s="15" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
@@ -3558,7 +3635,8 @@
       </c>
       <c r="L62" s="7" t="n"/>
       <c r="M62" s="8" t="n"/>
-      <c r="N62" s="8" t="n"/>
+      <c r="N62" s="17" t="n"/>
+      <c r="O62" s="15" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
@@ -3612,7 +3690,8 @@
       </c>
       <c r="L63" s="7" t="n"/>
       <c r="M63" s="8" t="n"/>
-      <c r="N63" s="8" t="n"/>
+      <c r="N63" s="17" t="n"/>
+      <c r="O63" s="15" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
@@ -3654,7 +3733,8 @@
       </c>
       <c r="L64" s="7" t="n"/>
       <c r="M64" s="8" t="n"/>
-      <c r="N64" s="8" t="n"/>
+      <c r="N64" s="17" t="n"/>
+      <c r="O64" s="15" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
@@ -3696,7 +3776,8 @@
       </c>
       <c r="L65" s="7" t="n"/>
       <c r="M65" s="8" t="n"/>
-      <c r="N65" s="8" t="n"/>
+      <c r="N65" s="17" t="n"/>
+      <c r="O65" s="15" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
@@ -3738,7 +3819,8 @@
       </c>
       <c r="L66" s="7" t="n"/>
       <c r="M66" s="8" t="n"/>
-      <c r="N66" s="8" t="n"/>
+      <c r="N66" s="17" t="n"/>
+      <c r="O66" s="15" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
@@ -3792,7 +3874,8 @@
       </c>
       <c r="L67" s="7" t="n"/>
       <c r="M67" s="8" t="n"/>
-      <c r="N67" s="8" t="n"/>
+      <c r="N67" s="17" t="n"/>
+      <c r="O67" s="15" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
@@ -3834,7 +3917,8 @@
       </c>
       <c r="L68" s="7" t="n"/>
       <c r="M68" s="8" t="n"/>
-      <c r="N68" s="8" t="n"/>
+      <c r="N68" s="17" t="n"/>
+      <c r="O68" s="15" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
@@ -3888,7 +3972,8 @@
       </c>
       <c r="L69" s="7" t="n"/>
       <c r="M69" s="8" t="n"/>
-      <c r="N69" s="8" t="n"/>
+      <c r="N69" s="17" t="n"/>
+      <c r="O69" s="15" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
@@ -3930,7 +4015,8 @@
       </c>
       <c r="L70" s="7" t="n"/>
       <c r="M70" s="8" t="n"/>
-      <c r="N70" s="8" t="n"/>
+      <c r="N70" s="17" t="n"/>
+      <c r="O70" s="15" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
@@ -3984,7 +4070,8 @@
       </c>
       <c r="L71" s="7" t="n"/>
       <c r="M71" s="8" t="n"/>
-      <c r="N71" s="8" t="n"/>
+      <c r="N71" s="17" t="n"/>
+      <c r="O71" s="15" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
@@ -4038,7 +4125,8 @@
       </c>
       <c r="L72" s="7" t="n"/>
       <c r="M72" s="8" t="n"/>
-      <c r="N72" s="8" t="n"/>
+      <c r="N72" s="17" t="n"/>
+      <c r="O72" s="15" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
@@ -4092,7 +4180,8 @@
       </c>
       <c r="L73" s="7" t="n"/>
       <c r="M73" s="8" t="n"/>
-      <c r="N73" s="8" t="n"/>
+      <c r="N73" s="17" t="n"/>
+      <c r="O73" s="15" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
@@ -4134,7 +4223,8 @@
       </c>
       <c r="L74" s="7" t="n"/>
       <c r="M74" s="8" t="n"/>
-      <c r="N74" s="8" t="n"/>
+      <c r="N74" s="17" t="n"/>
+      <c r="O74" s="15" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
@@ -4176,7 +4266,8 @@
       </c>
       <c r="L75" s="7" t="n"/>
       <c r="M75" s="8" t="n"/>
-      <c r="N75" s="8" t="n"/>
+      <c r="N75" s="17" t="n"/>
+      <c r="O75" s="15" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
@@ -4218,7 +4309,8 @@
       </c>
       <c r="L76" s="7" t="n"/>
       <c r="M76" s="8" t="n"/>
-      <c r="N76" s="8" t="n"/>
+      <c r="N76" s="17" t="n"/>
+      <c r="O76" s="15" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
@@ -4260,7 +4352,8 @@
       </c>
       <c r="L77" s="7" t="n"/>
       <c r="M77" s="8" t="n"/>
-      <c r="N77" s="8" t="n"/>
+      <c r="N77" s="17" t="n"/>
+      <c r="O77" s="15" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
@@ -4302,7 +4395,8 @@
       </c>
       <c r="L78" s="7" t="n"/>
       <c r="M78" s="8" t="n"/>
-      <c r="N78" s="8" t="n"/>
+      <c r="N78" s="17" t="n"/>
+      <c r="O78" s="15" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
@@ -4344,7 +4438,8 @@
       </c>
       <c r="L79" s="7" t="n"/>
       <c r="M79" s="8" t="n"/>
-      <c r="N79" s="8" t="n"/>
+      <c r="N79" s="17" t="n"/>
+      <c r="O79" s="15" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
@@ -4386,7 +4481,8 @@
       </c>
       <c r="L80" s="7" t="n"/>
       <c r="M80" s="8" t="n"/>
-      <c r="N80" s="8" t="n"/>
+      <c r="N80" s="17" t="n"/>
+      <c r="O80" s="15" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
@@ -4440,7 +4536,8 @@
       </c>
       <c r="L81" s="7" t="n"/>
       <c r="M81" s="8" t="n"/>
-      <c r="N81" s="8" t="n"/>
+      <c r="N81" s="17" t="n"/>
+      <c r="O81" s="15" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
@@ -4482,7 +4579,8 @@
       </c>
       <c r="L82" s="7" t="n"/>
       <c r="M82" s="8" t="n"/>
-      <c r="N82" s="8" t="n"/>
+      <c r="N82" s="17" t="n"/>
+      <c r="O82" s="15" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
@@ -4524,7 +4622,8 @@
       </c>
       <c r="L83" s="7" t="n"/>
       <c r="M83" s="8" t="n"/>
-      <c r="N83" s="8" t="n"/>
+      <c r="N83" s="17" t="n"/>
+      <c r="O83" s="15" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
@@ -4578,7 +4677,8 @@
       </c>
       <c r="L84" s="7" t="n"/>
       <c r="M84" s="8" t="n"/>
-      <c r="N84" s="8" t="n"/>
+      <c r="N84" s="17" t="n"/>
+      <c r="O84" s="15" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
@@ -4620,7 +4720,8 @@
       </c>
       <c r="L85" s="7" t="n"/>
       <c r="M85" s="8" t="n"/>
-      <c r="N85" s="8" t="n"/>
+      <c r="N85" s="17" t="n"/>
+      <c r="O85" s="15" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
@@ -4662,7 +4763,8 @@
       </c>
       <c r="L86" s="7" t="n"/>
       <c r="M86" s="8" t="n"/>
-      <c r="N86" s="8" t="n"/>
+      <c r="N86" s="17" t="n"/>
+      <c r="O86" s="15" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
@@ -4704,7 +4806,8 @@
       </c>
       <c r="L87" s="7" t="n"/>
       <c r="M87" s="8" t="n"/>
-      <c r="N87" s="8" t="n"/>
+      <c r="N87" s="17" t="n"/>
+      <c r="O87" s="15" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
@@ -4746,7 +4849,8 @@
       </c>
       <c r="L88" s="7" t="n"/>
       <c r="M88" s="8" t="n"/>
-      <c r="N88" s="8" t="n"/>
+      <c r="N88" s="17" t="n"/>
+      <c r="O88" s="15" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
@@ -4788,7 +4892,8 @@
       </c>
       <c r="L89" s="7" t="n"/>
       <c r="M89" s="8" t="n"/>
-      <c r="N89" s="8" t="n"/>
+      <c r="N89" s="17" t="n"/>
+      <c r="O89" s="15" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
@@ -4830,7 +4935,8 @@
       </c>
       <c r="L90" s="7" t="n"/>
       <c r="M90" s="8" t="n"/>
-      <c r="N90" s="8" t="n"/>
+      <c r="N90" s="17" t="n"/>
+      <c r="O90" s="15" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
@@ -4872,7 +4978,8 @@
       </c>
       <c r="L91" s="7" t="n"/>
       <c r="M91" s="8" t="n"/>
-      <c r="N91" s="8" t="n"/>
+      <c r="N91" s="17" t="n"/>
+      <c r="O91" s="15" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
@@ -4914,7 +5021,8 @@
       </c>
       <c r="L92" s="7" t="n"/>
       <c r="M92" s="8" t="n"/>
-      <c r="N92" s="8" t="n"/>
+      <c r="N92" s="17" t="n"/>
+      <c r="O92" s="15" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
@@ -4956,7 +5064,8 @@
       </c>
       <c r="L93" s="7" t="n"/>
       <c r="M93" s="8" t="n"/>
-      <c r="N93" s="8" t="n"/>
+      <c r="N93" s="17" t="n"/>
+      <c r="O93" s="15" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
@@ -4998,7 +5107,8 @@
       </c>
       <c r="L94" s="7" t="n"/>
       <c r="M94" s="8" t="n"/>
-      <c r="N94" s="8" t="n"/>
+      <c r="N94" s="17" t="n"/>
+      <c r="O94" s="15" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
@@ -5052,7 +5162,8 @@
       </c>
       <c r="L95" s="7" t="n"/>
       <c r="M95" s="8" t="n"/>
-      <c r="N95" s="8" t="n"/>
+      <c r="N95" s="17" t="n"/>
+      <c r="O95" s="15" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
@@ -5094,7 +5205,8 @@
       </c>
       <c r="L96" s="7" t="n"/>
       <c r="M96" s="8" t="n"/>
-      <c r="N96" s="8" t="n"/>
+      <c r="N96" s="17" t="n"/>
+      <c r="O96" s="15" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
@@ -5136,7 +5248,8 @@
       </c>
       <c r="L97" s="7" t="n"/>
       <c r="M97" s="8" t="n"/>
-      <c r="N97" s="8" t="n"/>
+      <c r="N97" s="17" t="n"/>
+      <c r="O97" s="15" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
@@ -5190,7 +5303,8 @@
       </c>
       <c r="L98" s="7" t="n"/>
       <c r="M98" s="8" t="n"/>
-      <c r="N98" s="8" t="n"/>
+      <c r="N98" s="17" t="n"/>
+      <c r="O98" s="15" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
@@ -5232,7 +5346,8 @@
       </c>
       <c r="L99" s="7" t="n"/>
       <c r="M99" s="8" t="n"/>
-      <c r="N99" s="8" t="n"/>
+      <c r="N99" s="17" t="n"/>
+      <c r="O99" s="15" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
@@ -5274,7 +5389,8 @@
       </c>
       <c r="L100" s="7" t="n"/>
       <c r="M100" s="8" t="n"/>
-      <c r="N100" s="8" t="n"/>
+      <c r="N100" s="17" t="n"/>
+      <c r="O100" s="15" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
@@ -5328,7 +5444,8 @@
       </c>
       <c r="L101" s="7" t="n"/>
       <c r="M101" s="8" t="n"/>
-      <c r="N101" s="8" t="n"/>
+      <c r="N101" s="17" t="n"/>
+      <c r="O101" s="15" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
@@ -5370,7 +5487,8 @@
       </c>
       <c r="L102" s="7" t="n"/>
       <c r="M102" s="8" t="n"/>
-      <c r="N102" s="8" t="n"/>
+      <c r="N102" s="17" t="n"/>
+      <c r="O102" s="15" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
@@ -5412,7 +5530,8 @@
       </c>
       <c r="L103" s="7" t="n"/>
       <c r="M103" s="8" t="n"/>
-      <c r="N103" s="8" t="n"/>
+      <c r="N103" s="17" t="n"/>
+      <c r="O103" s="15" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
@@ -5454,7 +5573,8 @@
       </c>
       <c r="L104" s="7" t="n"/>
       <c r="M104" s="8" t="n"/>
-      <c r="N104" s="8" t="n"/>
+      <c r="N104" s="17" t="n"/>
+      <c r="O104" s="15" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
@@ -5508,7 +5628,8 @@
       </c>
       <c r="L105" s="7" t="n"/>
       <c r="M105" s="8" t="n"/>
-      <c r="N105" s="8" t="n"/>
+      <c r="N105" s="17" t="n"/>
+      <c r="O105" s="15" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
@@ -5562,7 +5683,8 @@
       </c>
       <c r="L106" s="7" t="n"/>
       <c r="M106" s="8" t="n"/>
-      <c r="N106" s="8" t="n"/>
+      <c r="N106" s="17" t="n"/>
+      <c r="O106" s="15" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
@@ -5604,7 +5726,8 @@
       </c>
       <c r="L107" s="7" t="n"/>
       <c r="M107" s="8" t="n"/>
-      <c r="N107" s="8" t="n"/>
+      <c r="N107" s="17" t="n"/>
+      <c r="O107" s="15" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
@@ -5646,7 +5769,8 @@
       </c>
       <c r="L108" s="7" t="n"/>
       <c r="M108" s="8" t="n"/>
-      <c r="N108" s="8" t="n"/>
+      <c r="N108" s="17" t="n"/>
+      <c r="O108" s="15" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
@@ -5700,7 +5824,8 @@
       </c>
       <c r="L109" s="7" t="n"/>
       <c r="M109" s="8" t="n"/>
-      <c r="N109" s="8" t="n"/>
+      <c r="N109" s="17" t="n"/>
+      <c r="O109" s="15" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
@@ -5742,7 +5867,8 @@
       </c>
       <c r="L110" s="7" t="n"/>
       <c r="M110" s="8" t="n"/>
-      <c r="N110" s="8" t="n"/>
+      <c r="N110" s="17" t="n"/>
+      <c r="O110" s="15" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
@@ -5784,7 +5910,8 @@
       </c>
       <c r="L111" s="7" t="n"/>
       <c r="M111" s="8" t="n"/>
-      <c r="N111" s="8" t="n"/>
+      <c r="N111" s="17" t="n"/>
+      <c r="O111" s="15" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
@@ -5838,7 +5965,8 @@
       </c>
       <c r="L112" s="7" t="n"/>
       <c r="M112" s="8" t="n"/>
-      <c r="N112" s="8" t="n"/>
+      <c r="N112" s="17" t="n"/>
+      <c r="O112" s="15" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
@@ -5880,7 +6008,8 @@
       </c>
       <c r="L113" s="7" t="n"/>
       <c r="M113" s="8" t="n"/>
-      <c r="N113" s="8" t="n"/>
+      <c r="N113" s="17" t="n"/>
+      <c r="O113" s="15" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
@@ -5922,7 +6051,8 @@
       </c>
       <c r="L114" s="7" t="n"/>
       <c r="M114" s="8" t="n"/>
-      <c r="N114" s="8" t="n"/>
+      <c r="N114" s="17" t="n"/>
+      <c r="O114" s="15" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
@@ -5964,7 +6094,8 @@
       </c>
       <c r="L115" s="7" t="n"/>
       <c r="M115" s="8" t="n"/>
-      <c r="N115" s="8" t="n"/>
+      <c r="N115" s="17" t="n"/>
+      <c r="O115" s="15" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
@@ -6018,7 +6149,8 @@
       </c>
       <c r="L116" s="7" t="n"/>
       <c r="M116" s="8" t="n"/>
-      <c r="N116" s="8" t="n"/>
+      <c r="N116" s="17" t="n"/>
+      <c r="O116" s="15" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
@@ -6060,7 +6192,8 @@
       </c>
       <c r="L117" s="7" t="n"/>
       <c r="M117" s="8" t="n"/>
-      <c r="N117" s="8" t="n"/>
+      <c r="N117" s="17" t="n"/>
+      <c r="O117" s="15" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
@@ -6102,9 +6235,10 @@
       </c>
       <c r="L118" s="7" t="n"/>
       <c r="M118" s="8" t="n"/>
-      <c r="N118" s="8" t="n"/>
-    </row>
-    <row r="119" ht="26.4" customHeight="1" s="17">
+      <c r="N118" s="17" t="n"/>
+      <c r="O118" s="15" t="n"/>
+    </row>
+    <row r="119" ht="24.75" customHeight="1" s="20">
       <c r="A119" s="3" t="inlineStr">
         <is>
           <t>Telit_DOCCENTER.DbLib</t>
@@ -6147,23 +6281,23 @@
           <t>Please check alternative with better price and lead time</t>
         </is>
       </c>
-      <c r="M119" s="20" t="inlineStr">
-        <is>
-          <t>MAT-4265</t>
-        </is>
-      </c>
-      <c r="N119" s="8" t="inlineStr">
-        <is>
-          <t>Murata#GRM31CD71H106KE11L</t>
-        </is>
-      </c>
-      <c r="O119" s="0" t="inlineStr">
-        <is>
-          <t>MAT-4247</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="26.4" customHeight="1" s="17">
+      <c r="M119" s="22" t="inlineStr">
+        <is>
+          <t>MAT-4289</t>
+        </is>
+      </c>
+      <c r="N119" s="17" t="inlineStr">
+        <is>
+          <t>GRM31CD71H106KE11L</t>
+        </is>
+      </c>
+      <c r="O119" s="15" t="inlineStr">
+        <is>
+          <t>Murata</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="26.4" customHeight="1" s="20">
       <c r="A120" s="3" t="inlineStr">
         <is>
           <t>Telit_DOCCENTER.DbLib</t>
@@ -6206,19 +6340,19 @@
           <t>Please check alternative with better price and lead time</t>
         </is>
       </c>
-      <c r="M120" s="18" t="inlineStr">
-        <is>
-          <t>MAT-4258</t>
-        </is>
-      </c>
-      <c r="N120" s="8" t="inlineStr">
-        <is>
-          <t>Murata#GRM31CD71H106KE11L</t>
-        </is>
-      </c>
-      <c r="O120" s="0" t="inlineStr">
-        <is>
-          <t>MAT-4248</t>
+      <c r="M120" s="22" t="inlineStr">
+        <is>
+          <t>MAT-4289</t>
+        </is>
+      </c>
+      <c r="N120" s="17" t="inlineStr">
+        <is>
+          <t>GRM31CD71H106KE11L</t>
+        </is>
+      </c>
+      <c r="O120" s="15" t="inlineStr">
+        <is>
+          <t>Murata</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6408,8 @@
       </c>
       <c r="L121" s="7" t="n"/>
       <c r="M121" s="8" t="n"/>
-      <c r="N121" s="8" t="n"/>
+      <c r="N121" s="17" t="n"/>
+      <c r="O121" s="15" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
@@ -6316,7 +6451,8 @@
       </c>
       <c r="L122" s="7" t="n"/>
       <c r="M122" s="8" t="n"/>
-      <c r="N122" s="8" t="n"/>
+      <c r="N122" s="17" t="n"/>
+      <c r="O122" s="15" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
@@ -6370,7 +6506,8 @@
       </c>
       <c r="L123" s="7" t="n"/>
       <c r="M123" s="8" t="n"/>
-      <c r="N123" s="8" t="n"/>
+      <c r="N123" s="17" t="n"/>
+      <c r="O123" s="15" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
@@ -6412,7 +6549,8 @@
       </c>
       <c r="L124" s="7" t="n"/>
       <c r="M124" s="8" t="n"/>
-      <c r="N124" s="8" t="n"/>
+      <c r="N124" s="17" t="n"/>
+      <c r="O124" s="15" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
@@ -6454,7 +6592,8 @@
       </c>
       <c r="L125" s="7" t="n"/>
       <c r="M125" s="8" t="n"/>
-      <c r="N125" s="8" t="n"/>
+      <c r="N125" s="17" t="n"/>
+      <c r="O125" s="15" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
@@ -6508,7 +6647,8 @@
       </c>
       <c r="L126" s="7" t="n"/>
       <c r="M126" s="8" t="n"/>
-      <c r="N126" s="8" t="n"/>
+      <c r="N126" s="17" t="n"/>
+      <c r="O126" s="15" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
@@ -6550,7 +6690,8 @@
       </c>
       <c r="L127" s="7" t="n"/>
       <c r="M127" s="8" t="n"/>
-      <c r="N127" s="8" t="n"/>
+      <c r="N127" s="17" t="n"/>
+      <c r="O127" s="15" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
@@ -6592,7 +6733,8 @@
       </c>
       <c r="L128" s="7" t="n"/>
       <c r="M128" s="8" t="n"/>
-      <c r="N128" s="8" t="n"/>
+      <c r="N128" s="17" t="n"/>
+      <c r="O128" s="15" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
@@ -6634,7 +6776,8 @@
       </c>
       <c r="L129" s="7" t="n"/>
       <c r="M129" s="8" t="n"/>
-      <c r="N129" s="8" t="n"/>
+      <c r="N129" s="17" t="n"/>
+      <c r="O129" s="15" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
@@ -6676,7 +6819,8 @@
       </c>
       <c r="L130" s="7" t="n"/>
       <c r="M130" s="8" t="n"/>
-      <c r="N130" s="8" t="n"/>
+      <c r="N130" s="17" t="n"/>
+      <c r="O130" s="15" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
@@ -6730,7 +6874,8 @@
       </c>
       <c r="L131" s="7" t="n"/>
       <c r="M131" s="8" t="n"/>
-      <c r="N131" s="8" t="n"/>
+      <c r="N131" s="17" t="n"/>
+      <c r="O131" s="15" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
@@ -6784,7 +6929,8 @@
       </c>
       <c r="L132" s="7" t="n"/>
       <c r="M132" s="8" t="n"/>
-      <c r="N132" s="8" t="n"/>
+      <c r="N132" s="17" t="n"/>
+      <c r="O132" s="15" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
@@ -6826,7 +6972,8 @@
       </c>
       <c r="L133" s="7" t="n"/>
       <c r="M133" s="8" t="n"/>
-      <c r="N133" s="8" t="n"/>
+      <c r="N133" s="17" t="n"/>
+      <c r="O133" s="15" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
@@ -6868,7 +7015,8 @@
       </c>
       <c r="L134" s="7" t="n"/>
       <c r="M134" s="8" t="n"/>
-      <c r="N134" s="8" t="n"/>
+      <c r="N134" s="17" t="n"/>
+      <c r="O134" s="15" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
@@ -6910,7 +7058,8 @@
       </c>
       <c r="L135" s="7" t="n"/>
       <c r="M135" s="8" t="n"/>
-      <c r="N135" s="8" t="n"/>
+      <c r="N135" s="17" t="n"/>
+      <c r="O135" s="15" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
@@ -6952,7 +7101,8 @@
       </c>
       <c r="L136" s="7" t="n"/>
       <c r="M136" s="8" t="n"/>
-      <c r="N136" s="8" t="n"/>
+      <c r="N136" s="17" t="n"/>
+      <c r="O136" s="15" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
@@ -6994,7 +7144,8 @@
       </c>
       <c r="L137" s="7" t="n"/>
       <c r="M137" s="8" t="n"/>
-      <c r="N137" s="8" t="n"/>
+      <c r="N137" s="17" t="n"/>
+      <c r="O137" s="15" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
@@ -7048,7 +7199,8 @@
       </c>
       <c r="L138" s="7" t="n"/>
       <c r="M138" s="8" t="n"/>
-      <c r="N138" s="8" t="n"/>
+      <c r="N138" s="17" t="n"/>
+      <c r="O138" s="15" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
@@ -7090,7 +7242,8 @@
       </c>
       <c r="L139" s="7" t="n"/>
       <c r="M139" s="8" t="n"/>
-      <c r="N139" s="8" t="n"/>
+      <c r="N139" s="17" t="n"/>
+      <c r="O139" s="15" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
@@ -7132,7 +7285,8 @@
       </c>
       <c r="L140" s="7" t="n"/>
       <c r="M140" s="8" t="n"/>
-      <c r="N140" s="8" t="n"/>
+      <c r="N140" s="17" t="n"/>
+      <c r="O140" s="15" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
@@ -7174,7 +7328,8 @@
       </c>
       <c r="L141" s="7" t="n"/>
       <c r="M141" s="8" t="n"/>
-      <c r="N141" s="8" t="n"/>
+      <c r="N141" s="17" t="n"/>
+      <c r="O141" s="15" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
@@ -7216,7 +7371,8 @@
       </c>
       <c r="L142" s="7" t="n"/>
       <c r="M142" s="8" t="n"/>
-      <c r="N142" s="8" t="n"/>
+      <c r="N142" s="17" t="n"/>
+      <c r="O142" s="15" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
@@ -7270,7 +7426,8 @@
       </c>
       <c r="L143" s="7" t="n"/>
       <c r="M143" s="8" t="n"/>
-      <c r="N143" s="8" t="n"/>
+      <c r="N143" s="17" t="n"/>
+      <c r="O143" s="15" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
@@ -7312,7 +7469,8 @@
       </c>
       <c r="L144" s="7" t="n"/>
       <c r="M144" s="8" t="n"/>
-      <c r="N144" s="8" t="n"/>
+      <c r="N144" s="17" t="n"/>
+      <c r="O144" s="15" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
@@ -7354,7 +7512,8 @@
       </c>
       <c r="L145" s="7" t="n"/>
       <c r="M145" s="8" t="n"/>
-      <c r="N145" s="8" t="n"/>
+      <c r="N145" s="17" t="n"/>
+      <c r="O145" s="15" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
@@ -7396,7 +7555,8 @@
       </c>
       <c r="L146" s="7" t="n"/>
       <c r="M146" s="8" t="n"/>
-      <c r="N146" s="8" t="n"/>
+      <c r="N146" s="17" t="n"/>
+      <c r="O146" s="15" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
@@ -7438,7 +7598,8 @@
       </c>
       <c r="L147" s="7" t="n"/>
       <c r="M147" s="8" t="n"/>
-      <c r="N147" s="8" t="n"/>
+      <c r="N147" s="17" t="n"/>
+      <c r="O147" s="15" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
@@ -7492,7 +7653,8 @@
       </c>
       <c r="L148" s="7" t="n"/>
       <c r="M148" s="8" t="n"/>
-      <c r="N148" s="8" t="n"/>
+      <c r="N148" s="17" t="n"/>
+      <c r="O148" s="15" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
@@ -7546,7 +7708,8 @@
       </c>
       <c r="L149" s="7" t="n"/>
       <c r="M149" s="8" t="n"/>
-      <c r="N149" s="8" t="n"/>
+      <c r="N149" s="17" t="n"/>
+      <c r="O149" s="15" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
@@ -7588,7 +7751,8 @@
       </c>
       <c r="L150" s="7" t="n"/>
       <c r="M150" s="8" t="n"/>
-      <c r="N150" s="8" t="n"/>
+      <c r="N150" s="17" t="n"/>
+      <c r="O150" s="15" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
@@ -7642,7 +7806,8 @@
       </c>
       <c r="L151" s="7" t="n"/>
       <c r="M151" s="8" t="n"/>
-      <c r="N151" s="8" t="n"/>
+      <c r="N151" s="17" t="n"/>
+      <c r="O151" s="15" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
@@ -7696,7 +7861,8 @@
       </c>
       <c r="L152" s="7" t="n"/>
       <c r="M152" s="8" t="n"/>
-      <c r="N152" s="8" t="n"/>
+      <c r="N152" s="17" t="n"/>
+      <c r="O152" s="15" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
@@ -7738,7 +7904,8 @@
       </c>
       <c r="L153" s="7" t="n"/>
       <c r="M153" s="8" t="n"/>
-      <c r="N153" s="8" t="n"/>
+      <c r="N153" s="17" t="n"/>
+      <c r="O153" s="15" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
@@ -7780,7 +7947,8 @@
       </c>
       <c r="L154" s="7" t="n"/>
       <c r="M154" s="8" t="n"/>
-      <c r="N154" s="8" t="n"/>
+      <c r="N154" s="17" t="n"/>
+      <c r="O154" s="15" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
@@ -7822,7 +7990,8 @@
       </c>
       <c r="L155" s="7" t="n"/>
       <c r="M155" s="8" t="n"/>
-      <c r="N155" s="8" t="n"/>
+      <c r="N155" s="17" t="n"/>
+      <c r="O155" s="15" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
@@ -7864,7 +8033,8 @@
       </c>
       <c r="L156" s="7" t="n"/>
       <c r="M156" s="8" t="n"/>
-      <c r="N156" s="8" t="n"/>
+      <c r="N156" s="17" t="n"/>
+      <c r="O156" s="15" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
@@ -7906,7 +8076,8 @@
       </c>
       <c r="L157" s="7" t="n"/>
       <c r="M157" s="8" t="n"/>
-      <c r="N157" s="8" t="n"/>
+      <c r="N157" s="17" t="n"/>
+      <c r="O157" s="15" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
@@ -7948,7 +8119,8 @@
       </c>
       <c r="L158" s="7" t="n"/>
       <c r="M158" s="8" t="n"/>
-      <c r="N158" s="8" t="n"/>
+      <c r="N158" s="17" t="n"/>
+      <c r="O158" s="15" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
@@ -7990,7 +8162,8 @@
       </c>
       <c r="L159" s="7" t="n"/>
       <c r="M159" s="8" t="n"/>
-      <c r="N159" s="8" t="n"/>
+      <c r="N159" s="17" t="n"/>
+      <c r="O159" s="15" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
@@ -8032,7 +8205,8 @@
       </c>
       <c r="L160" s="7" t="n"/>
       <c r="M160" s="8" t="n"/>
-      <c r="N160" s="8" t="n"/>
+      <c r="N160" s="17" t="n"/>
+      <c r="O160" s="15" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
@@ -8074,7 +8248,8 @@
       </c>
       <c r="L161" s="7" t="n"/>
       <c r="M161" s="8" t="n"/>
-      <c r="N161" s="8" t="n"/>
+      <c r="N161" s="17" t="n"/>
+      <c r="O161" s="15" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
@@ -8116,7 +8291,8 @@
       </c>
       <c r="L162" s="7" t="n"/>
       <c r="M162" s="8" t="n"/>
-      <c r="N162" s="8" t="n"/>
+      <c r="N162" s="17" t="n"/>
+      <c r="O162" s="15" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
@@ -8158,7 +8334,8 @@
       </c>
       <c r="L163" s="7" t="n"/>
       <c r="M163" s="8" t="n"/>
-      <c r="N163" s="8" t="n"/>
+      <c r="N163" s="17" t="n"/>
+      <c r="O163" s="15" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
@@ -8200,7 +8377,8 @@
       </c>
       <c r="L164" s="7" t="n"/>
       <c r="M164" s="8" t="n"/>
-      <c r="N164" s="8" t="n"/>
+      <c r="N164" s="17" t="n"/>
+      <c r="O164" s="15" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
@@ -8242,7 +8420,8 @@
       </c>
       <c r="L165" s="7" t="n"/>
       <c r="M165" s="8" t="n"/>
-      <c r="N165" s="8" t="n"/>
+      <c r="N165" s="17" t="n"/>
+      <c r="O165" s="15" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
@@ -8284,7 +8463,8 @@
       </c>
       <c r="L166" s="7" t="n"/>
       <c r="M166" s="8" t="n"/>
-      <c r="N166" s="8" t="n"/>
+      <c r="N166" s="17" t="n"/>
+      <c r="O166" s="15" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
@@ -8326,7 +8506,8 @@
       </c>
       <c r="L167" s="7" t="n"/>
       <c r="M167" s="8" t="n"/>
-      <c r="N167" s="8" t="n"/>
+      <c r="N167" s="17" t="n"/>
+      <c r="O167" s="15" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
@@ -8368,7 +8549,8 @@
       </c>
       <c r="L168" s="7" t="n"/>
       <c r="M168" s="8" t="n"/>
-      <c r="N168" s="8" t="n"/>
+      <c r="N168" s="17" t="n"/>
+      <c r="O168" s="15" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
@@ -8410,7 +8592,8 @@
       </c>
       <c r="L169" s="7" t="n"/>
       <c r="M169" s="8" t="n"/>
-      <c r="N169" s="8" t="n"/>
+      <c r="N169" s="17" t="n"/>
+      <c r="O169" s="15" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
@@ -8452,9 +8635,10 @@
       </c>
       <c r="L170" s="7" t="n"/>
       <c r="M170" s="8" t="n"/>
-      <c r="N170" s="8" t="n"/>
-    </row>
-    <row r="171" ht="39.6" customHeight="1" s="17">
+      <c r="N170" s="17" t="n"/>
+      <c r="O170" s="15" t="n"/>
+    </row>
+    <row r="171" ht="39.6" customHeight="1" s="20">
       <c r="A171" s="3" t="inlineStr">
         <is>
           <t>Telit_DOCCENTER.DbLib</t>
@@ -8499,17 +8683,17 @@
       </c>
       <c r="M171" s="22" t="inlineStr">
         <is>
-          <t>MAT-4273</t>
-        </is>
-      </c>
-      <c r="N171" s="11" t="inlineStr">
+          <t>MAT-4290</t>
+        </is>
+      </c>
+      <c r="N171" s="18" t="inlineStr">
         <is>
           <t>V6R0B0402C0G500NBT</t>
         </is>
       </c>
-      <c r="O171" s="0" t="inlineStr">
-        <is>
-          <t>MAT-4249</t>
+      <c r="O171" s="15" t="inlineStr">
+        <is>
+          <t>VIIYONG</t>
         </is>
       </c>
     </row>
@@ -8553,7 +8737,8 @@
       </c>
       <c r="L172" s="7" t="n"/>
       <c r="M172" s="8" t="n"/>
-      <c r="N172" s="8" t="n"/>
+      <c r="N172" s="17" t="n"/>
+      <c r="O172" s="15" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
@@ -8595,7 +8780,8 @@
       </c>
       <c r="L173" s="7" t="n"/>
       <c r="M173" s="8" t="n"/>
-      <c r="N173" s="8" t="n"/>
+      <c r="N173" s="17" t="n"/>
+      <c r="O173" s="15" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
@@ -8637,7 +8823,8 @@
       </c>
       <c r="L174" s="7" t="n"/>
       <c r="M174" s="8" t="n"/>
-      <c r="N174" s="8" t="n"/>
+      <c r="N174" s="17" t="n"/>
+      <c r="O174" s="15" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
@@ -8679,7 +8866,8 @@
       </c>
       <c r="L175" s="7" t="n"/>
       <c r="M175" s="8" t="n"/>
-      <c r="N175" s="8" t="n"/>
+      <c r="N175" s="17" t="n"/>
+      <c r="O175" s="15" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
@@ -8721,7 +8909,8 @@
       </c>
       <c r="L176" s="7" t="n"/>
       <c r="M176" s="8" t="n"/>
-      <c r="N176" s="8" t="n"/>
+      <c r="N176" s="17" t="n"/>
+      <c r="O176" s="15" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
@@ -8763,7 +8952,8 @@
       </c>
       <c r="L177" s="7" t="n"/>
       <c r="M177" s="8" t="n"/>
-      <c r="N177" s="8" t="n"/>
+      <c r="N177" s="17" t="n"/>
+      <c r="O177" s="15" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
@@ -8805,7 +8995,8 @@
       </c>
       <c r="L178" s="7" t="n"/>
       <c r="M178" s="8" t="n"/>
-      <c r="N178" s="8" t="n"/>
+      <c r="N178" s="17" t="n"/>
+      <c r="O178" s="15" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
@@ -8847,7 +9038,8 @@
       </c>
       <c r="L179" s="7" t="n"/>
       <c r="M179" s="8" t="n"/>
-      <c r="N179" s="8" t="n"/>
+      <c r="N179" s="17" t="n"/>
+      <c r="O179" s="15" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
@@ -8901,7 +9093,8 @@
       </c>
       <c r="L180" s="7" t="n"/>
       <c r="M180" s="8" t="n"/>
-      <c r="N180" s="8" t="n"/>
+      <c r="N180" s="17" t="n"/>
+      <c r="O180" s="15" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
@@ -8955,7 +9148,8 @@
       </c>
       <c r="L181" s="7" t="n"/>
       <c r="M181" s="8" t="n"/>
-      <c r="N181" s="8" t="n"/>
+      <c r="N181" s="17" t="n"/>
+      <c r="O181" s="15" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
@@ -8997,7 +9191,8 @@
       </c>
       <c r="L182" s="7" t="n"/>
       <c r="M182" s="8" t="n"/>
-      <c r="N182" s="8" t="n"/>
+      <c r="N182" s="17" t="n"/>
+      <c r="O182" s="15" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
@@ -9039,7 +9234,8 @@
       </c>
       <c r="L183" s="7" t="n"/>
       <c r="M183" s="8" t="n"/>
-      <c r="N183" s="8" t="n"/>
+      <c r="N183" s="17" t="n"/>
+      <c r="O183" s="15" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
@@ -9093,7 +9289,8 @@
       </c>
       <c r="L184" s="7" t="n"/>
       <c r="M184" s="8" t="n"/>
-      <c r="N184" s="8" t="n"/>
+      <c r="N184" s="17" t="n"/>
+      <c r="O184" s="15" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
@@ -9135,7 +9332,8 @@
       </c>
       <c r="L185" s="7" t="n"/>
       <c r="M185" s="8" t="n"/>
-      <c r="N185" s="8" t="n"/>
+      <c r="N185" s="17" t="n"/>
+      <c r="O185" s="15" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
@@ -9177,7 +9375,8 @@
       </c>
       <c r="L186" s="7" t="n"/>
       <c r="M186" s="8" t="n"/>
-      <c r="N186" s="8" t="n"/>
+      <c r="N186" s="17" t="n"/>
+      <c r="O186" s="15" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
@@ -9219,7 +9418,8 @@
       </c>
       <c r="L187" s="7" t="n"/>
       <c r="M187" s="8" t="n"/>
-      <c r="N187" s="8" t="n"/>
+      <c r="N187" s="17" t="n"/>
+      <c r="O187" s="15" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
@@ -9261,7 +9461,8 @@
       </c>
       <c r="L188" s="7" t="n"/>
       <c r="M188" s="8" t="n"/>
-      <c r="N188" s="8" t="n"/>
+      <c r="N188" s="17" t="n"/>
+      <c r="O188" s="15" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
@@ -9303,7 +9504,8 @@
       </c>
       <c r="L189" s="7" t="n"/>
       <c r="M189" s="8" t="n"/>
-      <c r="N189" s="8" t="n"/>
+      <c r="N189" s="17" t="n"/>
+      <c r="O189" s="15" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
@@ -9345,7 +9547,8 @@
       </c>
       <c r="L190" s="7" t="n"/>
       <c r="M190" s="8" t="n"/>
-      <c r="N190" s="8" t="n"/>
+      <c r="N190" s="17" t="n"/>
+      <c r="O190" s="15" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
@@ -9387,7 +9590,8 @@
       </c>
       <c r="L191" s="7" t="n"/>
       <c r="M191" s="8" t="n"/>
-      <c r="N191" s="8" t="n"/>
+      <c r="N191" s="17" t="n"/>
+      <c r="O191" s="15" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
@@ -9429,7 +9633,8 @@
       </c>
       <c r="L192" s="7" t="n"/>
       <c r="M192" s="8" t="n"/>
-      <c r="N192" s="8" t="n"/>
+      <c r="N192" s="17" t="n"/>
+      <c r="O192" s="15" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
@@ -9471,7 +9676,8 @@
       </c>
       <c r="L193" s="7" t="n"/>
       <c r="M193" s="8" t="n"/>
-      <c r="N193" s="8" t="n"/>
+      <c r="N193" s="17" t="n"/>
+      <c r="O193" s="15" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
@@ -9513,7 +9719,8 @@
       </c>
       <c r="L194" s="7" t="n"/>
       <c r="M194" s="8" t="n"/>
-      <c r="N194" s="8" t="n"/>
+      <c r="N194" s="17" t="n"/>
+      <c r="O194" s="15" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
@@ -9555,7 +9762,8 @@
       </c>
       <c r="L195" s="7" t="n"/>
       <c r="M195" s="8" t="n"/>
-      <c r="N195" s="8" t="n"/>
+      <c r="N195" s="17" t="n"/>
+      <c r="O195" s="15" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
@@ -9597,7 +9805,8 @@
       </c>
       <c r="L196" s="7" t="n"/>
       <c r="M196" s="8" t="n"/>
-      <c r="N196" s="8" t="n"/>
+      <c r="N196" s="17" t="n"/>
+      <c r="O196" s="15" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="3" t="inlineStr">
@@ -9639,7 +9848,8 @@
       </c>
       <c r="L197" s="7" t="n"/>
       <c r="M197" s="8" t="n"/>
-      <c r="N197" s="8" t="n"/>
+      <c r="N197" s="17" t="n"/>
+      <c r="O197" s="15" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
@@ -9693,7 +9903,8 @@
       </c>
       <c r="L198" s="7" t="n"/>
       <c r="M198" s="8" t="n"/>
-      <c r="N198" s="8" t="n"/>
+      <c r="N198" s="17" t="n"/>
+      <c r="O198" s="15" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
@@ -9747,7 +9958,8 @@
       </c>
       <c r="L199" s="7" t="n"/>
       <c r="M199" s="8" t="n"/>
-      <c r="N199" s="8" t="n"/>
+      <c r="N199" s="17" t="n"/>
+      <c r="O199" s="15" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
@@ -9801,7 +10013,8 @@
       </c>
       <c r="L200" s="7" t="n"/>
       <c r="M200" s="8" t="n"/>
-      <c r="N200" s="8" t="n"/>
+      <c r="N200" s="17" t="n"/>
+      <c r="O200" s="15" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
@@ -9855,7 +10068,8 @@
       </c>
       <c r="L201" s="7" t="n"/>
       <c r="M201" s="8" t="n"/>
-      <c r="N201" s="8" t="n"/>
+      <c r="N201" s="17" t="n"/>
+      <c r="O201" s="15" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
@@ -9909,7 +10123,8 @@
       </c>
       <c r="L202" s="7" t="n"/>
       <c r="M202" s="8" t="n"/>
-      <c r="N202" s="8" t="n"/>
+      <c r="N202" s="17" t="n"/>
+      <c r="O202" s="15" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="3" t="inlineStr">
@@ -9963,7 +10178,8 @@
       </c>
       <c r="L203" s="7" t="n"/>
       <c r="M203" s="8" t="n"/>
-      <c r="N203" s="8" t="n"/>
+      <c r="N203" s="17" t="n"/>
+      <c r="O203" s="15" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="3" t="inlineStr">
@@ -10017,7 +10233,8 @@
       </c>
       <c r="L204" s="7" t="n"/>
       <c r="M204" s="8" t="n"/>
-      <c r="N204" s="8" t="n"/>
+      <c r="N204" s="17" t="n"/>
+      <c r="O204" s="15" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="3" t="inlineStr">
@@ -10071,7 +10288,8 @@
       </c>
       <c r="L205" s="7" t="n"/>
       <c r="M205" s="8" t="n"/>
-      <c r="N205" s="8" t="n"/>
+      <c r="N205" s="17" t="n"/>
+      <c r="O205" s="15" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
@@ -10125,7 +10343,8 @@
       </c>
       <c r="L206" s="7" t="n"/>
       <c r="M206" s="8" t="n"/>
-      <c r="N206" s="8" t="n"/>
+      <c r="N206" s="17" t="n"/>
+      <c r="O206" s="15" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="3" t="inlineStr">
@@ -10179,7 +10398,8 @@
       </c>
       <c r="L207" s="7" t="n"/>
       <c r="M207" s="8" t="n"/>
-      <c r="N207" s="8" t="n"/>
+      <c r="N207" s="17" t="n"/>
+      <c r="O207" s="15" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
@@ -10233,7 +10453,8 @@
       </c>
       <c r="L208" s="7" t="n"/>
       <c r="M208" s="8" t="n"/>
-      <c r="N208" s="8" t="n"/>
+      <c r="N208" s="17" t="n"/>
+      <c r="O208" s="15" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="3" t="inlineStr">
@@ -10287,7 +10508,8 @@
       </c>
       <c r="L209" s="7" t="n"/>
       <c r="M209" s="8" t="n"/>
-      <c r="N209" s="8" t="n"/>
+      <c r="N209" s="17" t="n"/>
+      <c r="O209" s="15" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="3" t="inlineStr">
@@ -10341,7 +10563,8 @@
       </c>
       <c r="L210" s="7" t="n"/>
       <c r="M210" s="8" t="n"/>
-      <c r="N210" s="8" t="n"/>
+      <c r="N210" s="17" t="n"/>
+      <c r="O210" s="15" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="3" t="inlineStr">
@@ -10395,7 +10618,8 @@
       </c>
       <c r="L211" s="7" t="n"/>
       <c r="M211" s="8" t="n"/>
-      <c r="N211" s="8" t="n"/>
+      <c r="N211" s="17" t="n"/>
+      <c r="O211" s="15" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="3" t="inlineStr">
@@ -10449,7 +10673,8 @@
       </c>
       <c r="L212" s="7" t="n"/>
       <c r="M212" s="8" t="n"/>
-      <c r="N212" s="8" t="n"/>
+      <c r="N212" s="17" t="n"/>
+      <c r="O212" s="15" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="3" t="inlineStr">
@@ -10503,7 +10728,8 @@
       </c>
       <c r="L213" s="7" t="n"/>
       <c r="M213" s="8" t="n"/>
-      <c r="N213" s="8" t="n"/>
+      <c r="N213" s="17" t="n"/>
+      <c r="O213" s="15" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="3" t="inlineStr">
@@ -10557,7 +10783,8 @@
       </c>
       <c r="L214" s="7" t="n"/>
       <c r="M214" s="8" t="n"/>
-      <c r="N214" s="8" t="n"/>
+      <c r="N214" s="17" t="n"/>
+      <c r="O214" s="15" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="3" t="inlineStr">
@@ -10611,7 +10838,8 @@
       </c>
       <c r="L215" s="7" t="n"/>
       <c r="M215" s="8" t="n"/>
-      <c r="N215" s="8" t="n"/>
+      <c r="N215" s="17" t="n"/>
+      <c r="O215" s="15" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
@@ -10665,7 +10893,8 @@
       </c>
       <c r="L216" s="7" t="n"/>
       <c r="M216" s="8" t="n"/>
-      <c r="N216" s="8" t="n"/>
+      <c r="N216" s="17" t="n"/>
+      <c r="O216" s="15" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="3" t="inlineStr">
@@ -10719,7 +10948,8 @@
       </c>
       <c r="L217" s="7" t="n"/>
       <c r="M217" s="8" t="n"/>
-      <c r="N217" s="8" t="n"/>
+      <c r="N217" s="17" t="n"/>
+      <c r="O217" s="15" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="3" t="inlineStr">
@@ -10773,7 +11003,8 @@
       </c>
       <c r="L218" s="7" t="n"/>
       <c r="M218" s="8" t="n"/>
-      <c r="N218" s="8" t="n"/>
+      <c r="N218" s="17" t="n"/>
+      <c r="O218" s="15" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="3" t="inlineStr">
@@ -10827,7 +11058,8 @@
       </c>
       <c r="L219" s="7" t="n"/>
       <c r="M219" s="8" t="n"/>
-      <c r="N219" s="8" t="n"/>
+      <c r="N219" s="17" t="n"/>
+      <c r="O219" s="15" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="3" t="inlineStr">
@@ -10881,7 +11113,8 @@
       </c>
       <c r="L220" s="7" t="n"/>
       <c r="M220" s="8" t="n"/>
-      <c r="N220" s="8" t="n"/>
+      <c r="N220" s="17" t="n"/>
+      <c r="O220" s="15" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="3" t="inlineStr">
@@ -10935,7 +11168,8 @@
       </c>
       <c r="L221" s="7" t="n"/>
       <c r="M221" s="8" t="n"/>
-      <c r="N221" s="8" t="n"/>
+      <c r="N221" s="17" t="n"/>
+      <c r="O221" s="15" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="3" t="inlineStr">
@@ -10989,7 +11223,8 @@
       </c>
       <c r="L222" s="7" t="n"/>
       <c r="M222" s="8" t="n"/>
-      <c r="N222" s="8" t="n"/>
+      <c r="N222" s="17" t="n"/>
+      <c r="O222" s="15" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="3" t="inlineStr">
@@ -11043,7 +11278,8 @@
       </c>
       <c r="L223" s="7" t="n"/>
       <c r="M223" s="8" t="n"/>
-      <c r="N223" s="8" t="n"/>
+      <c r="N223" s="17" t="n"/>
+      <c r="O223" s="15" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="3" t="inlineStr">
@@ -11097,7 +11333,8 @@
       </c>
       <c r="L224" s="7" t="n"/>
       <c r="M224" s="8" t="n"/>
-      <c r="N224" s="8" t="n"/>
+      <c r="N224" s="17" t="n"/>
+      <c r="O224" s="15" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="3" t="inlineStr">
@@ -11151,7 +11388,8 @@
       </c>
       <c r="L225" s="7" t="n"/>
       <c r="M225" s="8" t="n"/>
-      <c r="N225" s="8" t="n"/>
+      <c r="N225" s="17" t="n"/>
+      <c r="O225" s="15" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
@@ -11205,7 +11443,8 @@
       </c>
       <c r="L226" s="7" t="n"/>
       <c r="M226" s="8" t="n"/>
-      <c r="N226" s="8" t="n"/>
+      <c r="N226" s="17" t="n"/>
+      <c r="O226" s="15" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="3" t="inlineStr">
@@ -11259,7 +11498,8 @@
       </c>
       <c r="L227" s="7" t="n"/>
       <c r="M227" s="8" t="n"/>
-      <c r="N227" s="8" t="n"/>
+      <c r="N227" s="17" t="n"/>
+      <c r="O227" s="15" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="3" t="inlineStr">
@@ -11313,7 +11553,8 @@
       </c>
       <c r="L228" s="7" t="n"/>
       <c r="M228" s="8" t="n"/>
-      <c r="N228" s="8" t="n"/>
+      <c r="N228" s="17" t="n"/>
+      <c r="O228" s="15" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="3" t="inlineStr">
@@ -11367,9 +11608,10 @@
       </c>
       <c r="L229" s="7" t="n"/>
       <c r="M229" s="8" t="n"/>
-      <c r="N229" s="8" t="n"/>
-    </row>
-    <row r="230" ht="52.8" customHeight="1" s="17">
+      <c r="N229" s="17" t="n"/>
+      <c r="O229" s="15" t="n"/>
+    </row>
+    <row r="230" ht="52.95" customHeight="1" s="20">
       <c r="A230" s="3" t="inlineStr">
         <is>
           <t>Telit_DOCCENTER.DbLib</t>
@@ -11429,7 +11671,8 @@
           <t>1AA0700024BRN</t>
         </is>
       </c>
-      <c r="N230" s="8" t="n"/>
+      <c r="N230" s="17" t="n"/>
+      <c r="O230" s="15" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="3" t="inlineStr">
@@ -11483,7 +11726,8 @@
       </c>
       <c r="L231" s="7" t="n"/>
       <c r="M231" s="8" t="n"/>
-      <c r="N231" s="8" t="n"/>
+      <c r="N231" s="17" t="n"/>
+      <c r="O231" s="15" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="3" t="inlineStr">
@@ -11537,7 +11781,8 @@
       </c>
       <c r="L232" s="7" t="n"/>
       <c r="M232" s="8" t="n"/>
-      <c r="N232" s="8" t="n"/>
+      <c r="N232" s="17" t="n"/>
+      <c r="O232" s="15" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="3" t="inlineStr">
@@ -11591,7 +11836,8 @@
       </c>
       <c r="L233" s="7" t="n"/>
       <c r="M233" s="8" t="n"/>
-      <c r="N233" s="8" t="n"/>
+      <c r="N233" s="17" t="n"/>
+      <c r="O233" s="15" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
@@ -11645,7 +11891,8 @@
       </c>
       <c r="L234" s="7" t="n"/>
       <c r="M234" s="8" t="n"/>
-      <c r="N234" s="8" t="n"/>
+      <c r="N234" s="17" t="n"/>
+      <c r="O234" s="15" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="3" t="inlineStr">
@@ -11699,7 +11946,8 @@
       </c>
       <c r="L235" s="7" t="n"/>
       <c r="M235" s="8" t="n"/>
-      <c r="N235" s="8" t="n"/>
+      <c r="N235" s="17" t="n"/>
+      <c r="O235" s="15" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
@@ -11753,7 +12001,8 @@
       </c>
       <c r="L236" s="7" t="n"/>
       <c r="M236" s="8" t="n"/>
-      <c r="N236" s="8" t="n"/>
+      <c r="N236" s="17" t="n"/>
+      <c r="O236" s="15" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
@@ -11807,7 +12056,8 @@
       </c>
       <c r="L237" s="7" t="n"/>
       <c r="M237" s="8" t="n"/>
-      <c r="N237" s="8" t="n"/>
+      <c r="N237" s="17" t="n"/>
+      <c r="O237" s="15" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="3" t="inlineStr">
@@ -11861,7 +12111,8 @@
       </c>
       <c r="L238" s="7" t="n"/>
       <c r="M238" s="8" t="n"/>
-      <c r="N238" s="8" t="n"/>
+      <c r="N238" s="17" t="n"/>
+      <c r="O238" s="15" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="3" t="inlineStr">
@@ -11915,7 +12166,8 @@
       </c>
       <c r="L239" s="7" t="n"/>
       <c r="M239" s="8" t="n"/>
-      <c r="N239" s="8" t="n"/>
+      <c r="N239" s="17" t="n"/>
+      <c r="O239" s="15" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
@@ -11969,7 +12221,8 @@
       </c>
       <c r="L240" s="7" t="n"/>
       <c r="M240" s="8" t="n"/>
-      <c r="N240" s="8" t="n"/>
+      <c r="N240" s="17" t="n"/>
+      <c r="O240" s="15" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="3" t="inlineStr">
@@ -12019,7 +12272,8 @@
       </c>
       <c r="L241" s="7" t="n"/>
       <c r="M241" s="8" t="n"/>
-      <c r="N241" s="8" t="n"/>
+      <c r="N241" s="17" t="n"/>
+      <c r="O241" s="15" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="3" t="inlineStr">
@@ -12073,7 +12327,8 @@
       </c>
       <c r="L242" s="7" t="n"/>
       <c r="M242" s="8" t="n"/>
-      <c r="N242" s="8" t="n"/>
+      <c r="N242" s="17" t="n"/>
+      <c r="O242" s="15" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="3" t="inlineStr">
@@ -12130,21 +12385,17 @@
           <t>Please check alternative</t>
         </is>
       </c>
-      <c r="M243" s="20" t="inlineStr">
-        <is>
-          <t>MAT-4267</t>
-        </is>
-      </c>
-      <c r="N243" s="8" t="inlineStr">
+      <c r="M243" s="22" t="inlineStr">
+        <is>
+          <t>MAT-4291</t>
+        </is>
+      </c>
+      <c r="N243" s="17" t="inlineStr">
         <is>
           <t>Fenghua#VHF100505HQ6N2ST</t>
         </is>
       </c>
-      <c r="O243" s="0" t="inlineStr">
-        <is>
-          <t>MAT-4250</t>
-        </is>
-      </c>
+      <c r="O243" s="15" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="3" t="inlineStr">
@@ -12198,7 +12449,8 @@
       </c>
       <c r="L244" s="7" t="n"/>
       <c r="M244" s="8" t="n"/>
-      <c r="N244" s="8" t="n"/>
+      <c r="N244" s="17" t="n"/>
+      <c r="O244" s="15" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="3" t="inlineStr">
@@ -12252,7 +12504,8 @@
       </c>
       <c r="L245" s="7" t="n"/>
       <c r="M245" s="8" t="n"/>
-      <c r="N245" s="8" t="n"/>
+      <c r="N245" s="17" t="n"/>
+      <c r="O245" s="15" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="3" t="inlineStr">
@@ -12294,7 +12547,8 @@
       </c>
       <c r="L246" s="7" t="n"/>
       <c r="M246" s="8" t="n"/>
-      <c r="N246" s="8" t="n"/>
+      <c r="N246" s="17" t="n"/>
+      <c r="O246" s="15" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="3" t="inlineStr">
@@ -12336,7 +12590,8 @@
       </c>
       <c r="L247" s="7" t="n"/>
       <c r="M247" s="8" t="n"/>
-      <c r="N247" s="8" t="n"/>
+      <c r="N247" s="17" t="n"/>
+      <c r="O247" s="15" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="3" t="inlineStr">
@@ -12378,7 +12633,8 @@
       </c>
       <c r="L248" s="7" t="n"/>
       <c r="M248" s="8" t="n"/>
-      <c r="N248" s="8" t="n"/>
+      <c r="N248" s="17" t="n"/>
+      <c r="O248" s="15" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="3" t="inlineStr">
@@ -12432,7 +12688,8 @@
       </c>
       <c r="L249" s="7" t="n"/>
       <c r="M249" s="8" t="n"/>
-      <c r="N249" s="8" t="n"/>
+      <c r="N249" s="17" t="n"/>
+      <c r="O249" s="15" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="3" t="inlineStr">
@@ -12486,7 +12743,8 @@
       </c>
       <c r="L250" s="7" t="n"/>
       <c r="M250" s="8" t="n"/>
-      <c r="N250" s="8" t="n"/>
+      <c r="N250" s="17" t="n"/>
+      <c r="O250" s="15" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="3" t="inlineStr">
@@ -12540,7 +12798,8 @@
       </c>
       <c r="L251" s="7" t="n"/>
       <c r="M251" s="8" t="n"/>
-      <c r="N251" s="8" t="n"/>
+      <c r="N251" s="17" t="n"/>
+      <c r="O251" s="15" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="3" t="inlineStr">
@@ -12594,7 +12853,8 @@
       </c>
       <c r="L252" s="7" t="n"/>
       <c r="M252" s="8" t="n"/>
-      <c r="N252" s="8" t="n"/>
+      <c r="N252" s="17" t="n"/>
+      <c r="O252" s="15" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="3" t="inlineStr">
@@ -12648,7 +12908,8 @@
       </c>
       <c r="L253" s="7" t="n"/>
       <c r="M253" s="8" t="n"/>
-      <c r="N253" s="8" t="n"/>
+      <c r="N253" s="17" t="n"/>
+      <c r="O253" s="15" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="3" t="inlineStr">
@@ -12702,7 +12963,8 @@
       </c>
       <c r="L254" s="7" t="n"/>
       <c r="M254" s="8" t="n"/>
-      <c r="N254" s="8" t="n"/>
+      <c r="N254" s="17" t="n"/>
+      <c r="O254" s="15" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="3" t="inlineStr">
@@ -12756,9 +13018,10 @@
       </c>
       <c r="L255" s="7" t="n"/>
       <c r="M255" s="8" t="n"/>
-      <c r="N255" s="8" t="n"/>
-    </row>
-    <row r="256" ht="26.4" customHeight="1" s="17">
+      <c r="N255" s="17" t="n"/>
+      <c r="O255" s="15" t="n"/>
+    </row>
+    <row r="256" ht="26.4" customHeight="1" s="20">
       <c r="A256" s="3" t="inlineStr">
         <is>
           <t>Telit_DOCCENTER.DbLib</t>
@@ -12783,7 +13046,7 @@
           <t>L15</t>
         </is>
       </c>
-      <c r="G256" s="14" t="inlineStr">
+      <c r="G256" s="13" t="inlineStr">
         <is>
           <t>MURATA</t>
         </is>
@@ -12818,7 +13081,8 @@
           <t>Yes, updated</t>
         </is>
       </c>
-      <c r="N256" s="8" t="n"/>
+      <c r="N256" s="17" t="n"/>
+      <c r="O256" s="15" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="3" t="inlineStr">
@@ -12872,7 +13136,8 @@
       </c>
       <c r="L257" s="7" t="n"/>
       <c r="M257" s="8" t="n"/>
-      <c r="N257" s="8" t="n"/>
+      <c r="N257" s="17" t="n"/>
+      <c r="O257" s="15" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="3" t="inlineStr">
@@ -12926,7 +13191,8 @@
       </c>
       <c r="L258" s="7" t="n"/>
       <c r="M258" s="8" t="n"/>
-      <c r="N258" s="8" t="n"/>
+      <c r="N258" s="17" t="n"/>
+      <c r="O258" s="15" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="3" t="inlineStr">
@@ -12968,7 +13234,8 @@
       </c>
       <c r="L259" s="7" t="n"/>
       <c r="M259" s="8" t="n"/>
-      <c r="N259" s="8" t="n"/>
+      <c r="N259" s="17" t="n"/>
+      <c r="O259" s="15" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="3" t="inlineStr">
@@ -13022,7 +13289,8 @@
       </c>
       <c r="L260" s="7" t="n"/>
       <c r="M260" s="8" t="n"/>
-      <c r="N260" s="8" t="n"/>
+      <c r="N260" s="17" t="n"/>
+      <c r="O260" s="15" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="3" t="inlineStr">
@@ -13076,7 +13344,8 @@
       </c>
       <c r="L261" s="7" t="n"/>
       <c r="M261" s="8" t="n"/>
-      <c r="N261" s="8" t="n"/>
+      <c r="N261" s="17" t="n"/>
+      <c r="O261" s="15" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="3" t="inlineStr">
@@ -13130,7 +13399,8 @@
       </c>
       <c r="L262" s="7" t="n"/>
       <c r="M262" s="8" t="n"/>
-      <c r="N262" s="8" t="n"/>
+      <c r="N262" s="17" t="n"/>
+      <c r="O262" s="15" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="3" t="inlineStr">
@@ -13184,7 +13454,8 @@
       </c>
       <c r="L263" s="7" t="n"/>
       <c r="M263" s="8" t="n"/>
-      <c r="N263" s="8" t="n"/>
+      <c r="N263" s="17" t="n"/>
+      <c r="O263" s="15" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="3" t="inlineStr">
@@ -13238,7 +13509,8 @@
       </c>
       <c r="L264" s="7" t="n"/>
       <c r="M264" s="8" t="n"/>
-      <c r="N264" s="8" t="n"/>
+      <c r="N264" s="17" t="n"/>
+      <c r="O264" s="15" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="3" t="inlineStr">
@@ -13292,7 +13564,8 @@
       </c>
       <c r="L265" s="7" t="n"/>
       <c r="M265" s="8" t="n"/>
-      <c r="N265" s="8" t="n"/>
+      <c r="N265" s="17" t="n"/>
+      <c r="O265" s="15" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="3" t="inlineStr">
@@ -13346,7 +13619,8 @@
       </c>
       <c r="L266" s="7" t="n"/>
       <c r="M266" s="8" t="n"/>
-      <c r="N266" s="8" t="n"/>
+      <c r="N266" s="17" t="n"/>
+      <c r="O266" s="15" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="3" t="inlineStr">
@@ -13400,7 +13674,8 @@
       </c>
       <c r="L267" s="7" t="n"/>
       <c r="M267" s="8" t="n"/>
-      <c r="N267" s="8" t="n"/>
+      <c r="N267" s="17" t="n"/>
+      <c r="O267" s="15" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="3" t="inlineStr">
@@ -13454,7 +13729,8 @@
       </c>
       <c r="L268" s="7" t="n"/>
       <c r="M268" s="8" t="n"/>
-      <c r="N268" s="8" t="n"/>
+      <c r="N268" s="17" t="n"/>
+      <c r="O268" s="15" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="3" t="inlineStr">
@@ -13508,7 +13784,8 @@
       </c>
       <c r="L269" s="7" t="n"/>
       <c r="M269" s="8" t="n"/>
-      <c r="N269" s="8" t="n"/>
+      <c r="N269" s="17" t="n"/>
+      <c r="O269" s="15" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="3" t="inlineStr">
@@ -13562,7 +13839,8 @@
       </c>
       <c r="L270" s="7" t="n"/>
       <c r="M270" s="8" t="n"/>
-      <c r="N270" s="8" t="n"/>
+      <c r="N270" s="17" t="n"/>
+      <c r="O270" s="15" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="3" t="inlineStr">
@@ -13616,7 +13894,8 @@
       </c>
       <c r="L271" s="7" t="n"/>
       <c r="M271" s="8" t="n"/>
-      <c r="N271" s="8" t="n"/>
+      <c r="N271" s="17" t="n"/>
+      <c r="O271" s="15" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="3" t="inlineStr">
@@ -13670,7 +13949,8 @@
       </c>
       <c r="L272" s="7" t="n"/>
       <c r="M272" s="8" t="n"/>
-      <c r="N272" s="8" t="n"/>
+      <c r="N272" s="17" t="n"/>
+      <c r="O272" s="15" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="3" t="inlineStr">
@@ -13724,7 +14004,8 @@
       </c>
       <c r="L273" s="7" t="n"/>
       <c r="M273" s="8" t="n"/>
-      <c r="N273" s="8" t="n"/>
+      <c r="N273" s="17" t="n"/>
+      <c r="O273" s="15" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="3" t="inlineStr">
@@ -13778,7 +14059,8 @@
       </c>
       <c r="L274" s="7" t="n"/>
       <c r="M274" s="8" t="n"/>
-      <c r="N274" s="8" t="n"/>
+      <c r="N274" s="17" t="n"/>
+      <c r="O274" s="15" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="3" t="inlineStr">
@@ -13832,7 +14114,8 @@
       </c>
       <c r="L275" s="7" t="n"/>
       <c r="M275" s="8" t="n"/>
-      <c r="N275" s="8" t="n"/>
+      <c r="N275" s="17" t="n"/>
+      <c r="O275" s="15" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="3" t="inlineStr">
@@ -13886,7 +14169,8 @@
       </c>
       <c r="L276" s="7" t="n"/>
       <c r="M276" s="8" t="n"/>
-      <c r="N276" s="8" t="n"/>
+      <c r="N276" s="17" t="n"/>
+      <c r="O276" s="15" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="3" t="inlineStr">
@@ -13940,7 +14224,8 @@
       </c>
       <c r="L277" s="7" t="n"/>
       <c r="M277" s="8" t="n"/>
-      <c r="N277" s="8" t="n"/>
+      <c r="N277" s="17" t="n"/>
+      <c r="O277" s="15" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="3" t="inlineStr">
@@ -13994,7 +14279,8 @@
       </c>
       <c r="L278" s="7" t="n"/>
       <c r="M278" s="8" t="n"/>
-      <c r="N278" s="8" t="n"/>
+      <c r="N278" s="17" t="n"/>
+      <c r="O278" s="15" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="3" t="inlineStr">
@@ -14048,7 +14334,8 @@
       </c>
       <c r="L279" s="7" t="n"/>
       <c r="M279" s="8" t="n"/>
-      <c r="N279" s="8" t="n"/>
+      <c r="N279" s="17" t="n"/>
+      <c r="O279" s="15" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="3" t="inlineStr">
@@ -14102,7 +14389,8 @@
       </c>
       <c r="L280" s="7" t="n"/>
       <c r="M280" s="8" t="n"/>
-      <c r="N280" s="8" t="n"/>
+      <c r="N280" s="17" t="n"/>
+      <c r="O280" s="15" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="3" t="inlineStr">
@@ -14156,7 +14444,8 @@
       </c>
       <c r="L281" s="7" t="n"/>
       <c r="M281" s="8" t="n"/>
-      <c r="N281" s="8" t="n"/>
+      <c r="N281" s="17" t="n"/>
+      <c r="O281" s="15" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="3" t="inlineStr">
@@ -14210,7 +14499,8 @@
       </c>
       <c r="L282" s="7" t="n"/>
       <c r="M282" s="8" t="n"/>
-      <c r="N282" s="8" t="n"/>
+      <c r="N282" s="17" t="n"/>
+      <c r="O282" s="15" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="3" t="inlineStr">
@@ -14264,7 +14554,8 @@
       </c>
       <c r="L283" s="7" t="n"/>
       <c r="M283" s="8" t="n"/>
-      <c r="N283" s="8" t="n"/>
+      <c r="N283" s="17" t="n"/>
+      <c r="O283" s="15" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="3" t="inlineStr">
@@ -14318,7 +14609,8 @@
       </c>
       <c r="L284" s="7" t="n"/>
       <c r="M284" s="8" t="n"/>
-      <c r="N284" s="8" t="n"/>
+      <c r="N284" s="17" t="n"/>
+      <c r="O284" s="15" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="3" t="inlineStr">
@@ -14372,7 +14664,8 @@
       </c>
       <c r="L285" s="7" t="n"/>
       <c r="M285" s="8" t="n"/>
-      <c r="N285" s="8" t="n"/>
+      <c r="N285" s="17" t="n"/>
+      <c r="O285" s="15" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="3" t="inlineStr">
@@ -14425,12 +14718,9 @@
         </is>
       </c>
       <c r="L286" s="7" t="n"/>
-      <c r="M286" s="21" t="inlineStr">
-        <is>
-          <t>MAT-4268</t>
-        </is>
-      </c>
-      <c r="N286" s="8" t="n"/>
+      <c r="M286" s="8" t="n"/>
+      <c r="N286" s="17" t="n"/>
+      <c r="O286" s="15" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="3" t="inlineStr">
@@ -14484,7 +14774,8 @@
       </c>
       <c r="L287" s="7" t="n"/>
       <c r="M287" s="8" t="n"/>
-      <c r="N287" s="8" t="n"/>
+      <c r="N287" s="17" t="n"/>
+      <c r="O287" s="15" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="3" t="inlineStr">
@@ -14538,7 +14829,8 @@
       </c>
       <c r="L288" s="7" t="n"/>
       <c r="M288" s="8" t="n"/>
-      <c r="N288" s="8" t="n"/>
+      <c r="N288" s="17" t="n"/>
+      <c r="O288" s="15" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="3" t="inlineStr">
@@ -14592,7 +14884,8 @@
       </c>
       <c r="L289" s="7" t="n"/>
       <c r="M289" s="8" t="n"/>
-      <c r="N289" s="8" t="n"/>
+      <c r="N289" s="17" t="n"/>
+      <c r="O289" s="15" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="3" t="inlineStr">
@@ -14646,7 +14939,8 @@
       </c>
       <c r="L290" s="7" t="n"/>
       <c r="M290" s="8" t="n"/>
-      <c r="N290" s="8" t="n"/>
+      <c r="N290" s="17" t="n"/>
+      <c r="O290" s="15" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="3" t="inlineStr">
@@ -14700,7 +14994,8 @@
       </c>
       <c r="L291" s="7" t="n"/>
       <c r="M291" s="8" t="n"/>
-      <c r="N291" s="8" t="n"/>
+      <c r="N291" s="17" t="n"/>
+      <c r="O291" s="15" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="3" t="inlineStr">
@@ -14754,7 +15049,8 @@
       </c>
       <c r="L292" s="7" t="n"/>
       <c r="M292" s="8" t="n"/>
-      <c r="N292" s="8" t="n"/>
+      <c r="N292" s="17" t="n"/>
+      <c r="O292" s="15" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="3" t="inlineStr">
@@ -14808,7 +15104,8 @@
       </c>
       <c r="L293" s="7" t="n"/>
       <c r="M293" s="8" t="n"/>
-      <c r="N293" s="8" t="n"/>
+      <c r="N293" s="17" t="n"/>
+      <c r="O293" s="15" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="3" t="inlineStr">
@@ -14862,7 +15159,8 @@
       </c>
       <c r="L294" s="7" t="n"/>
       <c r="M294" s="8" t="n"/>
-      <c r="N294" s="8" t="n"/>
+      <c r="N294" s="17" t="n"/>
+      <c r="O294" s="15" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="3" t="inlineStr">
@@ -14916,7 +15214,8 @@
       </c>
       <c r="L295" s="7" t="n"/>
       <c r="M295" s="8" t="n"/>
-      <c r="N295" s="8" t="n"/>
+      <c r="N295" s="17" t="n"/>
+      <c r="O295" s="15" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="3" t="inlineStr">
@@ -14970,7 +15269,8 @@
       </c>
       <c r="L296" s="7" t="n"/>
       <c r="M296" s="8" t="n"/>
-      <c r="N296" s="8" t="n"/>
+      <c r="N296" s="17" t="n"/>
+      <c r="O296" s="15" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="3" t="inlineStr">
@@ -15024,7 +15324,8 @@
       </c>
       <c r="L297" s="7" t="n"/>
       <c r="M297" s="8" t="n"/>
-      <c r="N297" s="8" t="n"/>
+      <c r="N297" s="17" t="n"/>
+      <c r="O297" s="15" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="3" t="inlineStr">
@@ -15078,7 +15379,8 @@
       </c>
       <c r="L298" s="7" t="n"/>
       <c r="M298" s="8" t="n"/>
-      <c r="N298" s="8" t="n"/>
+      <c r="N298" s="17" t="n"/>
+      <c r="O298" s="15" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="3" t="inlineStr">
@@ -15132,7 +15434,8 @@
       </c>
       <c r="L299" s="7" t="n"/>
       <c r="M299" s="8" t="n"/>
-      <c r="N299" s="8" t="n"/>
+      <c r="N299" s="17" t="n"/>
+      <c r="O299" s="15" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="3" t="inlineStr">
@@ -15185,12 +15488,9 @@
         </is>
       </c>
       <c r="L300" s="7" t="n"/>
-      <c r="M300" s="19" t="inlineStr">
-        <is>
-          <t>MAT-4264</t>
-        </is>
-      </c>
-      <c r="N300" s="8" t="n"/>
+      <c r="M300" s="8" t="n"/>
+      <c r="N300" s="17" t="n"/>
+      <c r="O300" s="15" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="3" t="inlineStr">
@@ -15244,7 +15544,8 @@
       </c>
       <c r="L301" s="7" t="n"/>
       <c r="M301" s="8" t="n"/>
-      <c r="N301" s="8" t="n"/>
+      <c r="N301" s="17" t="n"/>
+      <c r="O301" s="15" t="n"/>
     </row>
     <row r="302">
       <c r="A302" s="3" t="inlineStr">
@@ -15298,7 +15599,8 @@
       </c>
       <c r="L302" s="7" t="n"/>
       <c r="M302" s="8" t="n"/>
-      <c r="N302" s="8" t="n"/>
+      <c r="N302" s="17" t="n"/>
+      <c r="O302" s="15" t="n"/>
     </row>
     <row r="303">
       <c r="A303" s="3" t="inlineStr">
@@ -15352,7 +15654,8 @@
       </c>
       <c r="L303" s="7" t="n"/>
       <c r="M303" s="8" t="n"/>
-      <c r="N303" s="8" t="n"/>
+      <c r="N303" s="17" t="n"/>
+      <c r="O303" s="15" t="n"/>
     </row>
     <row r="304">
       <c r="A304" s="3" t="inlineStr">
@@ -15406,7 +15709,8 @@
       </c>
       <c r="L304" s="7" t="n"/>
       <c r="M304" s="8" t="n"/>
-      <c r="N304" s="8" t="n"/>
+      <c r="N304" s="17" t="n"/>
+      <c r="O304" s="15" t="n"/>
     </row>
     <row r="305">
       <c r="A305" s="3" t="inlineStr">
@@ -15460,7 +15764,8 @@
       </c>
       <c r="L305" s="7" t="n"/>
       <c r="M305" s="8" t="n"/>
-      <c r="N305" s="8" t="n"/>
+      <c r="N305" s="17" t="n"/>
+      <c r="O305" s="15" t="n"/>
     </row>
     <row r="306">
       <c r="A306" s="3" t="inlineStr">
@@ -15514,7 +15819,8 @@
       </c>
       <c r="L306" s="7" t="n"/>
       <c r="M306" s="8" t="n"/>
-      <c r="N306" s="8" t="n"/>
+      <c r="N306" s="17" t="n"/>
+      <c r="O306" s="15" t="n"/>
     </row>
     <row r="307">
       <c r="A307" s="3" t="inlineStr">
@@ -15568,7 +15874,8 @@
       </c>
       <c r="L307" s="7" t="n"/>
       <c r="M307" s="8" t="n"/>
-      <c r="N307" s="8" t="n"/>
+      <c r="N307" s="17" t="n"/>
+      <c r="O307" s="15" t="n"/>
     </row>
     <row r="308">
       <c r="A308" s="3" t="inlineStr">
@@ -15610,7 +15917,8 @@
       </c>
       <c r="L308" s="7" t="n"/>
       <c r="M308" s="8" t="n"/>
-      <c r="N308" s="8" t="n"/>
+      <c r="N308" s="17" t="n"/>
+      <c r="O308" s="15" t="n"/>
     </row>
     <row r="309">
       <c r="A309" s="3" t="inlineStr">
@@ -15652,7 +15960,8 @@
       </c>
       <c r="L309" s="7" t="n"/>
       <c r="M309" s="8" t="n"/>
-      <c r="N309" s="8" t="n"/>
+      <c r="N309" s="17" t="n"/>
+      <c r="O309" s="15" t="n"/>
     </row>
     <row r="310">
       <c r="A310" s="3" t="inlineStr">
@@ -15706,7 +16015,8 @@
       </c>
       <c r="L310" s="7" t="n"/>
       <c r="M310" s="8" t="n"/>
-      <c r="N310" s="8" t="n"/>
+      <c r="N310" s="17" t="n"/>
+      <c r="O310" s="15" t="n"/>
     </row>
     <row r="311">
       <c r="A311" s="3" t="inlineStr">
@@ -15748,7 +16058,8 @@
       </c>
       <c r="L311" s="7" t="n"/>
       <c r="M311" s="8" t="n"/>
-      <c r="N311" s="8" t="n"/>
+      <c r="N311" s="17" t="n"/>
+      <c r="O311" s="15" t="n"/>
     </row>
     <row r="312">
       <c r="A312" s="3" t="inlineStr">
@@ -15802,7 +16113,8 @@
       </c>
       <c r="L312" s="7" t="n"/>
       <c r="M312" s="8" t="n"/>
-      <c r="N312" s="8" t="n"/>
+      <c r="N312" s="17" t="n"/>
+      <c r="O312" s="15" t="n"/>
     </row>
     <row r="313">
       <c r="A313" s="3" t="inlineStr">
@@ -15844,7 +16156,8 @@
       </c>
       <c r="L313" s="7" t="n"/>
       <c r="M313" s="8" t="n"/>
-      <c r="N313" s="8" t="n"/>
+      <c r="N313" s="17" t="n"/>
+      <c r="O313" s="15" t="n"/>
     </row>
     <row r="314">
       <c r="A314" s="3" t="inlineStr">
@@ -15898,7 +16211,8 @@
       </c>
       <c r="L314" s="7" t="n"/>
       <c r="M314" s="8" t="n"/>
-      <c r="N314" s="8" t="n"/>
+      <c r="N314" s="17" t="n"/>
+      <c r="O314" s="15" t="n"/>
     </row>
     <row r="315">
       <c r="A315" s="3" t="inlineStr">
@@ -15940,7 +16254,8 @@
       </c>
       <c r="L315" s="7" t="n"/>
       <c r="M315" s="8" t="n"/>
-      <c r="N315" s="8" t="n"/>
+      <c r="N315" s="17" t="n"/>
+      <c r="O315" s="15" t="n"/>
     </row>
     <row r="316">
       <c r="A316" s="3" t="inlineStr">
@@ -15982,7 +16297,8 @@
       </c>
       <c r="L316" s="7" t="n"/>
       <c r="M316" s="8" t="n"/>
-      <c r="N316" s="8" t="n"/>
+      <c r="N316" s="17" t="n"/>
+      <c r="O316" s="15" t="n"/>
     </row>
     <row r="317">
       <c r="A317" s="3" t="inlineStr">
@@ -16036,7 +16352,8 @@
       </c>
       <c r="L317" s="7" t="n"/>
       <c r="M317" s="8" t="n"/>
-      <c r="N317" s="8" t="n"/>
+      <c r="N317" s="17" t="n"/>
+      <c r="O317" s="15" t="n"/>
     </row>
     <row r="318">
       <c r="A318" s="3" t="inlineStr">
@@ -16090,7 +16407,8 @@
       </c>
       <c r="L318" s="7" t="n"/>
       <c r="M318" s="8" t="n"/>
-      <c r="N318" s="8" t="n"/>
+      <c r="N318" s="17" t="n"/>
+      <c r="O318" s="15" t="n"/>
     </row>
     <row r="319">
       <c r="A319" s="3" t="inlineStr">
@@ -16132,7 +16450,8 @@
       </c>
       <c r="L319" s="7" t="n"/>
       <c r="M319" s="8" t="n"/>
-      <c r="N319" s="8" t="n"/>
+      <c r="N319" s="17" t="n"/>
+      <c r="O319" s="15" t="n"/>
     </row>
     <row r="320">
       <c r="A320" s="3" t="inlineStr">
@@ -16186,7 +16505,8 @@
       </c>
       <c r="L320" s="7" t="n"/>
       <c r="M320" s="8" t="n"/>
-      <c r="N320" s="8" t="n"/>
+      <c r="N320" s="17" t="n"/>
+      <c r="O320" s="15" t="n"/>
     </row>
     <row r="321">
       <c r="A321" s="3" t="inlineStr">
@@ -16240,7 +16560,8 @@
       </c>
       <c r="L321" s="7" t="n"/>
       <c r="M321" s="8" t="n"/>
-      <c r="N321" s="8" t="n"/>
+      <c r="N321" s="17" t="n"/>
+      <c r="O321" s="15" t="n"/>
     </row>
     <row r="322">
       <c r="A322" s="3" t="inlineStr">
@@ -16294,7 +16615,8 @@
       </c>
       <c r="L322" s="7" t="n"/>
       <c r="M322" s="8" t="n"/>
-      <c r="N322" s="8" t="n"/>
+      <c r="N322" s="17" t="n"/>
+      <c r="O322" s="15" t="n"/>
     </row>
     <row r="323">
       <c r="A323" s="3" t="inlineStr">
@@ -16336,7 +16658,8 @@
       </c>
       <c r="L323" s="7" t="n"/>
       <c r="M323" s="8" t="n"/>
-      <c r="N323" s="8" t="n"/>
+      <c r="N323" s="17" t="n"/>
+      <c r="O323" s="15" t="n"/>
     </row>
     <row r="324">
       <c r="A324" s="3" t="inlineStr">
@@ -16378,7 +16701,8 @@
       </c>
       <c r="L324" s="7" t="n"/>
       <c r="M324" s="8" t="n"/>
-      <c r="N324" s="8" t="n"/>
+      <c r="N324" s="17" t="n"/>
+      <c r="O324" s="15" t="n"/>
     </row>
     <row r="325">
       <c r="A325" s="3" t="inlineStr">
@@ -16420,7 +16744,8 @@
       </c>
       <c r="L325" s="7" t="n"/>
       <c r="M325" s="8" t="n"/>
-      <c r="N325" s="8" t="n"/>
+      <c r="N325" s="17" t="n"/>
+      <c r="O325" s="15" t="n"/>
     </row>
     <row r="326">
       <c r="A326" s="3" t="inlineStr">
@@ -16462,7 +16787,8 @@
       </c>
       <c r="L326" s="7" t="n"/>
       <c r="M326" s="8" t="n"/>
-      <c r="N326" s="8" t="n"/>
+      <c r="N326" s="17" t="n"/>
+      <c r="O326" s="15" t="n"/>
     </row>
     <row r="327">
       <c r="A327" s="3" t="inlineStr">
@@ -16516,7 +16842,8 @@
       </c>
       <c r="L327" s="7" t="n"/>
       <c r="M327" s="8" t="n"/>
-      <c r="N327" s="8" t="n"/>
+      <c r="N327" s="17" t="n"/>
+      <c r="O327" s="15" t="n"/>
     </row>
     <row r="328">
       <c r="A328" s="3" t="inlineStr">
@@ -16570,7 +16897,8 @@
       </c>
       <c r="L328" s="7" t="n"/>
       <c r="M328" s="8" t="n"/>
-      <c r="N328" s="8" t="n"/>
+      <c r="N328" s="17" t="n"/>
+      <c r="O328" s="15" t="n"/>
     </row>
     <row r="329">
       <c r="A329" s="3" t="inlineStr">
@@ -16624,7 +16952,8 @@
       </c>
       <c r="L329" s="7" t="n"/>
       <c r="M329" s="8" t="n"/>
-      <c r="N329" s="8" t="n"/>
+      <c r="N329" s="17" t="n"/>
+      <c r="O329" s="15" t="n"/>
     </row>
     <row r="330">
       <c r="A330" s="3" t="inlineStr">
@@ -16678,7 +17007,8 @@
       </c>
       <c r="L330" s="7" t="n"/>
       <c r="M330" s="8" t="n"/>
-      <c r="N330" s="8" t="n"/>
+      <c r="N330" s="17" t="n"/>
+      <c r="O330" s="15" t="n"/>
     </row>
     <row r="331">
       <c r="A331" s="3" t="inlineStr">
@@ -16732,7 +17062,8 @@
       </c>
       <c r="L331" s="7" t="n"/>
       <c r="M331" s="8" t="n"/>
-      <c r="N331" s="8" t="n"/>
+      <c r="N331" s="17" t="n"/>
+      <c r="O331" s="15" t="n"/>
     </row>
     <row r="332">
       <c r="A332" s="3" t="inlineStr">
@@ -16774,7 +17105,8 @@
       </c>
       <c r="L332" s="7" t="n"/>
       <c r="M332" s="8" t="n"/>
-      <c r="N332" s="8" t="n"/>
+      <c r="N332" s="17" t="n"/>
+      <c r="O332" s="15" t="n"/>
     </row>
     <row r="333">
       <c r="A333" s="3" t="inlineStr">
@@ -16816,7 +17148,8 @@
       </c>
       <c r="L333" s="7" t="n"/>
       <c r="M333" s="8" t="n"/>
-      <c r="N333" s="8" t="n"/>
+      <c r="N333" s="17" t="n"/>
+      <c r="O333" s="15" t="n"/>
     </row>
     <row r="334">
       <c r="A334" s="3" t="inlineStr">
@@ -16858,7 +17191,8 @@
       </c>
       <c r="L334" s="7" t="n"/>
       <c r="M334" s="8" t="n"/>
-      <c r="N334" s="8" t="n"/>
+      <c r="N334" s="17" t="n"/>
+      <c r="O334" s="15" t="n"/>
     </row>
     <row r="335">
       <c r="A335" s="3" t="inlineStr">
@@ -16900,7 +17234,8 @@
       </c>
       <c r="L335" s="7" t="n"/>
       <c r="M335" s="8" t="n"/>
-      <c r="N335" s="8" t="n"/>
+      <c r="N335" s="17" t="n"/>
+      <c r="O335" s="15" t="n"/>
     </row>
     <row r="336">
       <c r="A336" s="3" t="inlineStr">
@@ -16954,7 +17289,8 @@
       </c>
       <c r="L336" s="7" t="n"/>
       <c r="M336" s="8" t="n"/>
-      <c r="N336" s="8" t="n"/>
+      <c r="N336" s="17" t="n"/>
+      <c r="O336" s="15" t="n"/>
     </row>
     <row r="337">
       <c r="A337" s="3" t="inlineStr">
@@ -17008,7 +17344,8 @@
       </c>
       <c r="L337" s="7" t="n"/>
       <c r="M337" s="8" t="n"/>
-      <c r="N337" s="8" t="n"/>
+      <c r="N337" s="17" t="n"/>
+      <c r="O337" s="15" t="n"/>
     </row>
     <row r="338">
       <c r="A338" s="3" t="inlineStr">
@@ -17062,7 +17399,8 @@
       </c>
       <c r="L338" s="7" t="n"/>
       <c r="M338" s="8" t="n"/>
-      <c r="N338" s="8" t="n"/>
+      <c r="N338" s="17" t="n"/>
+      <c r="O338" s="15" t="n"/>
     </row>
     <row r="339">
       <c r="A339" s="3" t="inlineStr">
@@ -17116,7 +17454,8 @@
       </c>
       <c r="L339" s="7" t="n"/>
       <c r="M339" s="8" t="n"/>
-      <c r="N339" s="8" t="n"/>
+      <c r="N339" s="17" t="n"/>
+      <c r="O339" s="15" t="n"/>
     </row>
     <row r="340">
       <c r="A340" s="3" t="inlineStr">
@@ -17170,7 +17509,8 @@
       </c>
       <c r="L340" s="7" t="n"/>
       <c r="M340" s="8" t="n"/>
-      <c r="N340" s="8" t="n"/>
+      <c r="N340" s="17" t="n"/>
+      <c r="O340" s="15" t="n"/>
     </row>
     <row r="341">
       <c r="A341" s="3" t="inlineStr">
@@ -17212,7 +17552,8 @@
       </c>
       <c r="L341" s="7" t="n"/>
       <c r="M341" s="8" t="n"/>
-      <c r="N341" s="8" t="n"/>
+      <c r="N341" s="17" t="n"/>
+      <c r="O341" s="15" t="n"/>
     </row>
     <row r="342">
       <c r="A342" s="3" t="inlineStr">
@@ -17266,7 +17607,8 @@
       </c>
       <c r="L342" s="7" t="n"/>
       <c r="M342" s="8" t="n"/>
-      <c r="N342" s="8" t="n"/>
+      <c r="N342" s="17" t="n"/>
+      <c r="O342" s="15" t="n"/>
     </row>
     <row r="343">
       <c r="A343" s="3" t="inlineStr">
@@ -17320,7 +17662,8 @@
       </c>
       <c r="L343" s="7" t="n"/>
       <c r="M343" s="8" t="n"/>
-      <c r="N343" s="8" t="n"/>
+      <c r="N343" s="17" t="n"/>
+      <c r="O343" s="15" t="n"/>
     </row>
     <row r="344">
       <c r="A344" s="3" t="inlineStr">
@@ -17374,7 +17717,8 @@
       </c>
       <c r="L344" s="7" t="n"/>
       <c r="M344" s="8" t="n"/>
-      <c r="N344" s="8" t="n"/>
+      <c r="N344" s="17" t="n"/>
+      <c r="O344" s="15" t="n"/>
     </row>
     <row r="345">
       <c r="A345" s="3" t="inlineStr">
@@ -17428,7 +17772,8 @@
       </c>
       <c r="L345" s="7" t="n"/>
       <c r="M345" s="8" t="n"/>
-      <c r="N345" s="8" t="n"/>
+      <c r="N345" s="17" t="n"/>
+      <c r="O345" s="15" t="n"/>
     </row>
     <row r="346">
       <c r="A346" s="3" t="inlineStr">
@@ -17486,11 +17831,12 @@
           <t>MAT-4224</t>
         </is>
       </c>
-      <c r="N346" s="11" t="inlineStr">
+      <c r="N346" s="18" t="inlineStr">
         <is>
           <t>FENGHUA - MFJ06HR010FT</t>
         </is>
       </c>
+      <c r="O346" s="15" t="n"/>
     </row>
     <row r="347">
       <c r="A347" s="3" t="inlineStr">
@@ -17544,7 +17890,8 @@
       </c>
       <c r="L347" s="7" t="n"/>
       <c r="M347" s="8" t="n"/>
-      <c r="N347" s="8" t="n"/>
+      <c r="N347" s="17" t="n"/>
+      <c r="O347" s="15" t="n"/>
     </row>
     <row r="348">
       <c r="A348" s="3" t="inlineStr">
@@ -17586,7 +17933,8 @@
       </c>
       <c r="L348" s="7" t="n"/>
       <c r="M348" s="8" t="n"/>
-      <c r="N348" s="8" t="n"/>
+      <c r="N348" s="17" t="n"/>
+      <c r="O348" s="15" t="n"/>
     </row>
     <row r="349">
       <c r="A349" s="3" t="inlineStr">
@@ -17640,7 +17988,8 @@
       </c>
       <c r="L349" s="7" t="n"/>
       <c r="M349" s="8" t="n"/>
-      <c r="N349" s="8" t="n"/>
+      <c r="N349" s="17" t="n"/>
+      <c r="O349" s="15" t="n"/>
     </row>
     <row r="350">
       <c r="A350" s="3" t="inlineStr">
@@ -17682,7 +18031,8 @@
       </c>
       <c r="L350" s="7" t="n"/>
       <c r="M350" s="8" t="n"/>
-      <c r="N350" s="8" t="n"/>
+      <c r="N350" s="17" t="n"/>
+      <c r="O350" s="15" t="n"/>
     </row>
     <row r="351">
       <c r="A351" s="3" t="inlineStr">
@@ -17724,7 +18074,8 @@
       </c>
       <c r="L351" s="7" t="n"/>
       <c r="M351" s="8" t="n"/>
-      <c r="N351" s="8" t="n"/>
+      <c r="N351" s="17" t="n"/>
+      <c r="O351" s="15" t="n"/>
     </row>
     <row r="352">
       <c r="A352" s="3" t="inlineStr">
@@ -17766,7 +18117,8 @@
       </c>
       <c r="L352" s="7" t="n"/>
       <c r="M352" s="8" t="n"/>
-      <c r="N352" s="8" t="n"/>
+      <c r="N352" s="17" t="n"/>
+      <c r="O352" s="15" t="n"/>
     </row>
     <row r="353">
       <c r="A353" s="3" t="inlineStr">
@@ -17808,7 +18160,8 @@
       </c>
       <c r="L353" s="7" t="n"/>
       <c r="M353" s="8" t="n"/>
-      <c r="N353" s="8" t="n"/>
+      <c r="N353" s="17" t="n"/>
+      <c r="O353" s="15" t="n"/>
     </row>
     <row r="354">
       <c r="A354" s="3" t="inlineStr">
@@ -17862,7 +18215,8 @@
       </c>
       <c r="L354" s="7" t="n"/>
       <c r="M354" s="8" t="n"/>
-      <c r="N354" s="8" t="n"/>
+      <c r="N354" s="17" t="n"/>
+      <c r="O354" s="15" t="n"/>
     </row>
     <row r="355">
       <c r="A355" s="3" t="inlineStr">
@@ -17916,9 +18270,10 @@
       </c>
       <c r="L355" s="7" t="n"/>
       <c r="M355" s="8" t="n"/>
-      <c r="N355" s="8" t="n"/>
-    </row>
-    <row r="356" ht="26.4" customHeight="1" s="17">
+      <c r="N355" s="17" t="n"/>
+      <c r="O355" s="15" t="n"/>
+    </row>
+    <row r="356" ht="26.4" customHeight="1" s="20">
       <c r="A356" s="3" t="inlineStr">
         <is>
           <t>Telit_DOCCENTER.DbLib</t>
@@ -17961,12 +18316,13 @@
           <t>MAT-4222</t>
         </is>
       </c>
-      <c r="N356" s="10" t="inlineStr">
+      <c r="N356" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">WALSIN	 - WR04X2700FTL
 FENGHUA - RC-02K2700FT　</t>
         </is>
       </c>
+      <c r="O356" s="15" t="n"/>
     </row>
     <row r="357">
       <c r="A357" s="3" t="inlineStr">
@@ -18008,7 +18364,8 @@
       </c>
       <c r="L357" s="7" t="n"/>
       <c r="M357" s="8" t="n"/>
-      <c r="N357" s="8" t="n"/>
+      <c r="N357" s="17" t="n"/>
+      <c r="O357" s="15" t="n"/>
     </row>
     <row r="358">
       <c r="A358" s="3" t="inlineStr">
@@ -18050,7 +18407,8 @@
       </c>
       <c r="L358" s="7" t="n"/>
       <c r="M358" s="8" t="n"/>
-      <c r="N358" s="8" t="n"/>
+      <c r="N358" s="17" t="n"/>
+      <c r="O358" s="15" t="n"/>
     </row>
     <row r="359">
       <c r="A359" s="3" t="inlineStr">
@@ -18092,7 +18450,8 @@
       </c>
       <c r="L359" s="7" t="n"/>
       <c r="M359" s="8" t="n"/>
-      <c r="N359" s="8" t="n"/>
+      <c r="N359" s="17" t="n"/>
+      <c r="O359" s="15" t="n"/>
     </row>
     <row r="360">
       <c r="A360" s="3" t="inlineStr">
@@ -18134,7 +18493,8 @@
       </c>
       <c r="L360" s="7" t="n"/>
       <c r="M360" s="8" t="n"/>
-      <c r="N360" s="8" t="n"/>
+      <c r="N360" s="17" t="n"/>
+      <c r="O360" s="15" t="n"/>
     </row>
     <row r="361">
       <c r="A361" s="3" t="inlineStr">
@@ -18176,7 +18536,8 @@
       </c>
       <c r="L361" s="7" t="n"/>
       <c r="M361" s="8" t="n"/>
-      <c r="N361" s="8" t="n"/>
+      <c r="N361" s="17" t="n"/>
+      <c r="O361" s="15" t="n"/>
     </row>
     <row r="362">
       <c r="A362" s="3" t="inlineStr">
@@ -18218,7 +18579,8 @@
       </c>
       <c r="L362" s="7" t="n"/>
       <c r="M362" s="8" t="n"/>
-      <c r="N362" s="8" t="n"/>
+      <c r="N362" s="17" t="n"/>
+      <c r="O362" s="15" t="n"/>
     </row>
     <row r="363">
       <c r="A363" s="3" t="inlineStr">
@@ -18272,7 +18634,8 @@
       </c>
       <c r="L363" s="7" t="n"/>
       <c r="M363" s="8" t="n"/>
-      <c r="N363" s="8" t="n"/>
+      <c r="N363" s="17" t="n"/>
+      <c r="O363" s="15" t="n"/>
     </row>
     <row r="364">
       <c r="A364" s="3" t="inlineStr">
@@ -18326,7 +18689,8 @@
       </c>
       <c r="L364" s="7" t="n"/>
       <c r="M364" s="8" t="n"/>
-      <c r="N364" s="8" t="n"/>
+      <c r="N364" s="17" t="n"/>
+      <c r="O364" s="15" t="n"/>
     </row>
     <row r="365">
       <c r="A365" s="3" t="inlineStr">
@@ -18368,7 +18732,8 @@
       </c>
       <c r="L365" s="7" t="n"/>
       <c r="M365" s="8" t="n"/>
-      <c r="N365" s="8" t="n"/>
+      <c r="N365" s="17" t="n"/>
+      <c r="O365" s="15" t="n"/>
     </row>
     <row r="366">
       <c r="A366" s="3" t="inlineStr">
@@ -18422,7 +18787,8 @@
       </c>
       <c r="L366" s="7" t="n"/>
       <c r="M366" s="8" t="n"/>
-      <c r="N366" s="8" t="n"/>
+      <c r="N366" s="17" t="n"/>
+      <c r="O366" s="15" t="n"/>
     </row>
     <row r="367">
       <c r="A367" s="3" t="inlineStr">
@@ -18476,7 +18842,8 @@
       </c>
       <c r="L367" s="7" t="n"/>
       <c r="M367" s="8" t="n"/>
-      <c r="N367" s="8" t="n"/>
+      <c r="N367" s="17" t="n"/>
+      <c r="O367" s="15" t="n"/>
     </row>
     <row r="368">
       <c r="A368" s="3" t="inlineStr">
@@ -18518,7 +18885,8 @@
       </c>
       <c r="L368" s="7" t="n"/>
       <c r="M368" s="8" t="n"/>
-      <c r="N368" s="8" t="n"/>
+      <c r="N368" s="17" t="n"/>
+      <c r="O368" s="15" t="n"/>
     </row>
     <row r="369">
       <c r="A369" s="3" t="inlineStr">
@@ -18560,7 +18928,8 @@
       </c>
       <c r="L369" s="7" t="n"/>
       <c r="M369" s="8" t="n"/>
-      <c r="N369" s="8" t="n"/>
+      <c r="N369" s="17" t="n"/>
+      <c r="O369" s="15" t="n"/>
     </row>
     <row r="370">
       <c r="A370" s="3" t="inlineStr">
@@ -18602,7 +18971,8 @@
       </c>
       <c r="L370" s="7" t="n"/>
       <c r="M370" s="8" t="n"/>
-      <c r="N370" s="8" t="n"/>
+      <c r="N370" s="17" t="n"/>
+      <c r="O370" s="15" t="n"/>
     </row>
     <row r="371">
       <c r="A371" s="3" t="inlineStr">
@@ -18644,7 +19014,8 @@
       </c>
       <c r="L371" s="7" t="n"/>
       <c r="M371" s="8" t="n"/>
-      <c r="N371" s="8" t="n"/>
+      <c r="N371" s="17" t="n"/>
+      <c r="O371" s="15" t="n"/>
     </row>
     <row r="372">
       <c r="A372" s="3" t="inlineStr">
@@ -18698,7 +19069,8 @@
       </c>
       <c r="L372" s="7" t="n"/>
       <c r="M372" s="8" t="n"/>
-      <c r="N372" s="8" t="n"/>
+      <c r="N372" s="17" t="n"/>
+      <c r="O372" s="15" t="n"/>
     </row>
     <row r="373">
       <c r="A373" s="3" t="inlineStr">
@@ -18752,7 +19124,8 @@
       </c>
       <c r="L373" s="7" t="n"/>
       <c r="M373" s="8" t="n"/>
-      <c r="N373" s="8" t="n"/>
+      <c r="N373" s="17" t="n"/>
+      <c r="O373" s="15" t="n"/>
     </row>
     <row r="374">
       <c r="A374" s="3" t="inlineStr">
@@ -18794,7 +19167,8 @@
       </c>
       <c r="L374" s="7" t="n"/>
       <c r="M374" s="8" t="n"/>
-      <c r="N374" s="8" t="n"/>
+      <c r="N374" s="17" t="n"/>
+      <c r="O374" s="15" t="n"/>
     </row>
     <row r="375">
       <c r="A375" s="3" t="inlineStr">
@@ -18848,7 +19222,8 @@
       </c>
       <c r="L375" s="7" t="n"/>
       <c r="M375" s="8" t="n"/>
-      <c r="N375" s="8" t="n"/>
+      <c r="N375" s="17" t="n"/>
+      <c r="O375" s="15" t="n"/>
     </row>
     <row r="376">
       <c r="A376" s="3" t="inlineStr">
@@ -18902,7 +19277,8 @@
       </c>
       <c r="L376" s="7" t="n"/>
       <c r="M376" s="8" t="n"/>
-      <c r="N376" s="8" t="n"/>
+      <c r="N376" s="17" t="n"/>
+      <c r="O376" s="15" t="n"/>
     </row>
     <row r="377">
       <c r="A377" s="3" t="inlineStr">
@@ -18944,7 +19320,8 @@
       </c>
       <c r="L377" s="7" t="n"/>
       <c r="M377" s="8" t="n"/>
-      <c r="N377" s="8" t="n"/>
+      <c r="N377" s="17" t="n"/>
+      <c r="O377" s="15" t="n"/>
     </row>
     <row r="378">
       <c r="A378" s="3" t="inlineStr">
@@ -18986,7 +19363,8 @@
       </c>
       <c r="L378" s="7" t="n"/>
       <c r="M378" s="8" t="n"/>
-      <c r="N378" s="8" t="n"/>
+      <c r="N378" s="17" t="n"/>
+      <c r="O378" s="15" t="n"/>
     </row>
     <row r="379">
       <c r="A379" s="3" t="inlineStr">
@@ -19028,7 +19406,8 @@
       </c>
       <c r="L379" s="7" t="n"/>
       <c r="M379" s="8" t="n"/>
-      <c r="N379" s="8" t="n"/>
+      <c r="N379" s="17" t="n"/>
+      <c r="O379" s="15" t="n"/>
     </row>
     <row r="380">
       <c r="A380" s="3" t="inlineStr">
@@ -19070,7 +19449,8 @@
       </c>
       <c r="L380" s="7" t="n"/>
       <c r="M380" s="8" t="n"/>
-      <c r="N380" s="8" t="n"/>
+      <c r="N380" s="17" t="n"/>
+      <c r="O380" s="15" t="n"/>
     </row>
     <row r="381">
       <c r="A381" s="3" t="inlineStr">
@@ -19112,7 +19492,8 @@
       </c>
       <c r="L381" s="7" t="n"/>
       <c r="M381" s="8" t="n"/>
-      <c r="N381" s="8" t="n"/>
+      <c r="N381" s="17" t="n"/>
+      <c r="O381" s="15" t="n"/>
     </row>
     <row r="382">
       <c r="A382" s="3" t="inlineStr">
@@ -19154,7 +19535,8 @@
       </c>
       <c r="L382" s="7" t="n"/>
       <c r="M382" s="8" t="n"/>
-      <c r="N382" s="8" t="n"/>
+      <c r="N382" s="17" t="n"/>
+      <c r="O382" s="15" t="n"/>
     </row>
     <row r="383">
       <c r="A383" s="3" t="inlineStr">
@@ -19196,7 +19578,8 @@
       </c>
       <c r="L383" s="7" t="n"/>
       <c r="M383" s="8" t="n"/>
-      <c r="N383" s="8" t="n"/>
+      <c r="N383" s="17" t="n"/>
+      <c r="O383" s="15" t="n"/>
     </row>
     <row r="384">
       <c r="A384" s="3" t="inlineStr">
@@ -19238,7 +19621,8 @@
       </c>
       <c r="L384" s="7" t="n"/>
       <c r="M384" s="8" t="n"/>
-      <c r="N384" s="8" t="n"/>
+      <c r="N384" s="17" t="n"/>
+      <c r="O384" s="15" t="n"/>
     </row>
     <row r="385">
       <c r="A385" s="3" t="inlineStr">
@@ -19280,7 +19664,8 @@
       </c>
       <c r="L385" s="7" t="n"/>
       <c r="M385" s="8" t="n"/>
-      <c r="N385" s="8" t="n"/>
+      <c r="N385" s="17" t="n"/>
+      <c r="O385" s="15" t="n"/>
     </row>
     <row r="386">
       <c r="A386" s="3" t="inlineStr">
@@ -19322,7 +19707,8 @@
       </c>
       <c r="L386" s="7" t="n"/>
       <c r="M386" s="8" t="n"/>
-      <c r="N386" s="8" t="n"/>
+      <c r="N386" s="17" t="n"/>
+      <c r="O386" s="15" t="n"/>
     </row>
     <row r="387">
       <c r="A387" s="3" t="inlineStr">
@@ -19364,7 +19750,8 @@
       </c>
       <c r="L387" s="7" t="n"/>
       <c r="M387" s="8" t="n"/>
-      <c r="N387" s="8" t="n"/>
+      <c r="N387" s="17" t="n"/>
+      <c r="O387" s="15" t="n"/>
     </row>
     <row r="388">
       <c r="A388" s="3" t="inlineStr">
@@ -19406,7 +19793,8 @@
       </c>
       <c r="L388" s="7" t="n"/>
       <c r="M388" s="8" t="n"/>
-      <c r="N388" s="8" t="n"/>
+      <c r="N388" s="17" t="n"/>
+      <c r="O388" s="15" t="n"/>
     </row>
     <row r="389">
       <c r="A389" s="3" t="inlineStr">
@@ -19448,7 +19836,8 @@
       </c>
       <c r="L389" s="7" t="n"/>
       <c r="M389" s="8" t="n"/>
-      <c r="N389" s="8" t="n"/>
+      <c r="N389" s="17" t="n"/>
+      <c r="O389" s="15" t="n"/>
     </row>
     <row r="390">
       <c r="A390" s="3" t="inlineStr">
@@ -19490,7 +19879,8 @@
       </c>
       <c r="L390" s="7" t="n"/>
       <c r="M390" s="8" t="n"/>
-      <c r="N390" s="8" t="n"/>
+      <c r="N390" s="17" t="n"/>
+      <c r="O390" s="15" t="n"/>
     </row>
     <row r="391">
       <c r="A391" s="3" t="inlineStr">
@@ -19532,7 +19922,8 @@
       </c>
       <c r="L391" s="7" t="n"/>
       <c r="M391" s="8" t="n"/>
-      <c r="N391" s="8" t="n"/>
+      <c r="N391" s="17" t="n"/>
+      <c r="O391" s="15" t="n"/>
     </row>
     <row r="392">
       <c r="A392" s="3" t="inlineStr">
@@ -19574,7 +19965,8 @@
       </c>
       <c r="L392" s="7" t="n"/>
       <c r="M392" s="8" t="n"/>
-      <c r="N392" s="8" t="n"/>
+      <c r="N392" s="17" t="n"/>
+      <c r="O392" s="15" t="n"/>
     </row>
     <row r="393">
       <c r="A393" s="3" t="inlineStr">
@@ -19616,7 +20008,8 @@
       </c>
       <c r="L393" s="7" t="n"/>
       <c r="M393" s="8" t="n"/>
-      <c r="N393" s="8" t="n"/>
+      <c r="N393" s="17" t="n"/>
+      <c r="O393" s="15" t="n"/>
     </row>
     <row r="394">
       <c r="A394" s="3" t="inlineStr">
@@ -19658,7 +20051,8 @@
       </c>
       <c r="L394" s="7" t="n"/>
       <c r="M394" s="8" t="n"/>
-      <c r="N394" s="8" t="n"/>
+      <c r="N394" s="17" t="n"/>
+      <c r="O394" s="15" t="n"/>
     </row>
     <row r="395">
       <c r="A395" s="3" t="inlineStr">
@@ -19700,7 +20094,8 @@
       </c>
       <c r="L395" s="7" t="n"/>
       <c r="M395" s="8" t="n"/>
-      <c r="N395" s="8" t="n"/>
+      <c r="N395" s="17" t="n"/>
+      <c r="O395" s="15" t="n"/>
     </row>
     <row r="396">
       <c r="A396" s="3" t="inlineStr">
@@ -19742,7 +20137,8 @@
       </c>
       <c r="L396" s="7" t="n"/>
       <c r="M396" s="8" t="n"/>
-      <c r="N396" s="8" t="n"/>
+      <c r="N396" s="17" t="n"/>
+      <c r="O396" s="15" t="n"/>
     </row>
     <row r="397">
       <c r="A397" s="3" t="inlineStr">
@@ -19784,7 +20180,8 @@
       </c>
       <c r="L397" s="7" t="n"/>
       <c r="M397" s="8" t="n"/>
-      <c r="N397" s="8" t="n"/>
+      <c r="N397" s="17" t="n"/>
+      <c r="O397" s="15" t="n"/>
     </row>
     <row r="398">
       <c r="A398" s="3" t="inlineStr">
@@ -19826,7 +20223,8 @@
       </c>
       <c r="L398" s="7" t="n"/>
       <c r="M398" s="8" t="n"/>
-      <c r="N398" s="8" t="n"/>
+      <c r="N398" s="17" t="n"/>
+      <c r="O398" s="15" t="n"/>
     </row>
     <row r="399">
       <c r="A399" s="3" t="inlineStr">
@@ -19868,7 +20266,8 @@
       </c>
       <c r="L399" s="7" t="n"/>
       <c r="M399" s="8" t="n"/>
-      <c r="N399" s="8" t="n"/>
+      <c r="N399" s="17" t="n"/>
+      <c r="O399" s="15" t="n"/>
     </row>
     <row r="400">
       <c r="A400" s="3" t="inlineStr">
@@ -19910,7 +20309,8 @@
       </c>
       <c r="L400" s="7" t="n"/>
       <c r="M400" s="8" t="n"/>
-      <c r="N400" s="8" t="n"/>
+      <c r="N400" s="17" t="n"/>
+      <c r="O400" s="15" t="n"/>
     </row>
     <row r="401">
       <c r="A401" s="3" t="inlineStr">
@@ -19952,9 +20352,10 @@
       </c>
       <c r="L401" s="7" t="n"/>
       <c r="M401" s="8" t="n"/>
-      <c r="N401" s="8" t="n"/>
-    </row>
-    <row r="402" ht="26.4" customHeight="1" s="17">
+      <c r="N401" s="17" t="n"/>
+      <c r="O401" s="15" t="n"/>
+    </row>
+    <row r="402" ht="26.4" customHeight="1" s="20">
       <c r="A402" s="3" t="inlineStr">
         <is>
           <t>Telit_DOCCENTER.DbLib</t>
@@ -19997,12 +20398,13 @@
           <t>MAT-4220</t>
         </is>
       </c>
-      <c r="N402" s="10" t="inlineStr">
+      <c r="N402" s="19" t="inlineStr">
         <is>
           <t>WALSIN	 - WR04X564 JTL
 FENGHUA - RC-02K564JT</t>
         </is>
       </c>
+      <c r="O402" s="15" t="n"/>
     </row>
     <row r="403">
       <c r="A403" s="3" t="inlineStr">
@@ -20044,9 +20446,10 @@
       </c>
       <c r="L403" s="7" t="n"/>
       <c r="M403" s="8" t="n"/>
-      <c r="N403" s="8" t="n"/>
-    </row>
-    <row r="404" ht="26.4" customHeight="1" s="17">
+      <c r="N403" s="17" t="n"/>
+      <c r="O403" s="15" t="n"/>
+    </row>
+    <row r="404" ht="26.4" customHeight="1" s="20">
       <c r="A404" s="3" t="inlineStr">
         <is>
           <t>Telit_DOCCENTER.DbLib</t>
@@ -20089,12 +20492,13 @@
           <t>MAT-4221</t>
         </is>
       </c>
-      <c r="N404" s="10" t="inlineStr">
+      <c r="N404" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">WALSIN	 - WR04X4223FTL
 FENGHUA - RC-02K4223FT　</t>
         </is>
       </c>
+      <c r="O404" s="15" t="n"/>
     </row>
     <row r="405">
       <c r="A405" s="3" t="inlineStr">
@@ -20136,7 +20540,8 @@
       </c>
       <c r="L405" s="7" t="n"/>
       <c r="M405" s="8" t="n"/>
-      <c r="N405" s="8" t="n"/>
+      <c r="N405" s="17" t="n"/>
+      <c r="O405" s="15" t="n"/>
     </row>
     <row r="406">
       <c r="A406" s="3" t="inlineStr">
@@ -20178,7 +20583,8 @@
       </c>
       <c r="L406" s="7" t="n"/>
       <c r="M406" s="8" t="n"/>
-      <c r="N406" s="8" t="n"/>
+      <c r="N406" s="17" t="n"/>
+      <c r="O406" s="15" t="n"/>
     </row>
     <row r="407">
       <c r="A407" s="3" t="inlineStr">
@@ -20220,7 +20626,8 @@
       </c>
       <c r="L407" s="7" t="n"/>
       <c r="M407" s="8" t="n"/>
-      <c r="N407" s="8" t="n"/>
+      <c r="N407" s="17" t="n"/>
+      <c r="O407" s="15" t="n"/>
     </row>
     <row r="408">
       <c r="A408" s="3" t="inlineStr">
@@ -20262,7 +20669,8 @@
       </c>
       <c r="L408" s="7" t="n"/>
       <c r="M408" s="8" t="n"/>
-      <c r="N408" s="8" t="n"/>
+      <c r="N408" s="17" t="n"/>
+      <c r="O408" s="15" t="n"/>
     </row>
     <row r="409">
       <c r="A409" s="3" t="inlineStr">
@@ -20304,7 +20712,8 @@
       </c>
       <c r="L409" s="7" t="n"/>
       <c r="M409" s="8" t="n"/>
-      <c r="N409" s="8" t="n"/>
+      <c r="N409" s="17" t="n"/>
+      <c r="O409" s="15" t="n"/>
     </row>
     <row r="410">
       <c r="A410" s="3" t="inlineStr">
@@ -20346,7 +20755,8 @@
       </c>
       <c r="L410" s="7" t="n"/>
       <c r="M410" s="8" t="n"/>
-      <c r="N410" s="8" t="n"/>
+      <c r="N410" s="17" t="n"/>
+      <c r="O410" s="15" t="n"/>
     </row>
     <row r="411">
       <c r="A411" s="3" t="inlineStr">
@@ -20388,7 +20798,8 @@
       </c>
       <c r="L411" s="7" t="n"/>
       <c r="M411" s="8" t="n"/>
-      <c r="N411" s="8" t="n"/>
+      <c r="N411" s="17" t="n"/>
+      <c r="O411" s="15" t="n"/>
     </row>
     <row r="412">
       <c r="A412" s="3" t="inlineStr">
@@ -20430,7 +20841,8 @@
       </c>
       <c r="L412" s="7" t="n"/>
       <c r="M412" s="8" t="n"/>
-      <c r="N412" s="8" t="n"/>
+      <c r="N412" s="17" t="n"/>
+      <c r="O412" s="15" t="n"/>
     </row>
     <row r="413">
       <c r="A413" s="3" t="inlineStr">
@@ -20472,7 +20884,8 @@
       </c>
       <c r="L413" s="7" t="n"/>
       <c r="M413" s="8" t="n"/>
-      <c r="N413" s="8" t="n"/>
+      <c r="N413" s="17" t="n"/>
+      <c r="O413" s="15" t="n"/>
     </row>
     <row r="414">
       <c r="A414" s="3" t="inlineStr">
@@ -20514,7 +20927,8 @@
       </c>
       <c r="L414" s="7" t="n"/>
       <c r="M414" s="8" t="n"/>
-      <c r="N414" s="8" t="n"/>
+      <c r="N414" s="17" t="n"/>
+      <c r="O414" s="15" t="n"/>
     </row>
     <row r="415">
       <c r="A415" s="3" t="inlineStr">
@@ -20556,7 +20970,8 @@
       </c>
       <c r="L415" s="7" t="n"/>
       <c r="M415" s="8" t="n"/>
-      <c r="N415" s="8" t="n"/>
+      <c r="N415" s="17" t="n"/>
+      <c r="O415" s="15" t="n"/>
     </row>
     <row r="416">
       <c r="A416" s="3" t="inlineStr">
@@ -20610,7 +21025,8 @@
       </c>
       <c r="L416" s="7" t="n"/>
       <c r="M416" s="8" t="n"/>
-      <c r="N416" s="8" t="n"/>
+      <c r="N416" s="17" t="n"/>
+      <c r="O416" s="15" t="n"/>
     </row>
     <row r="417">
       <c r="A417" s="3" t="inlineStr">
@@ -20664,7 +21080,8 @@
       </c>
       <c r="L417" s="7" t="n"/>
       <c r="M417" s="8" t="n"/>
-      <c r="N417" s="8" t="n"/>
+      <c r="N417" s="17" t="n"/>
+      <c r="O417" s="15" t="n"/>
     </row>
     <row r="418">
       <c r="A418" s="3" t="inlineStr">
@@ -20706,7 +21123,8 @@
       </c>
       <c r="L418" s="7" t="n"/>
       <c r="M418" s="8" t="n"/>
-      <c r="N418" s="8" t="n"/>
+      <c r="N418" s="17" t="n"/>
+      <c r="O418" s="15" t="n"/>
     </row>
     <row r="419">
       <c r="A419" s="3" t="inlineStr">
@@ -20760,7 +21178,8 @@
       </c>
       <c r="L419" s="7" t="n"/>
       <c r="M419" s="8" t="n"/>
-      <c r="N419" s="8" t="n"/>
+      <c r="N419" s="17" t="n"/>
+      <c r="O419" s="15" t="n"/>
     </row>
     <row r="420">
       <c r="A420" s="3" t="inlineStr">
@@ -20814,7 +21233,8 @@
       </c>
       <c r="L420" s="7" t="n"/>
       <c r="M420" s="8" t="n"/>
-      <c r="N420" s="8" t="n"/>
+      <c r="N420" s="17" t="n"/>
+      <c r="O420" s="15" t="n"/>
     </row>
     <row r="421">
       <c r="A421" s="3" t="inlineStr">
@@ -20856,7 +21276,8 @@
       </c>
       <c r="L421" s="7" t="n"/>
       <c r="M421" s="8" t="n"/>
-      <c r="N421" s="8" t="n"/>
+      <c r="N421" s="17" t="n"/>
+      <c r="O421" s="15" t="n"/>
     </row>
     <row r="422">
       <c r="A422" s="3" t="inlineStr">
@@ -20898,7 +21319,8 @@
       </c>
       <c r="L422" s="7" t="n"/>
       <c r="M422" s="8" t="n"/>
-      <c r="N422" s="8" t="n"/>
+      <c r="N422" s="17" t="n"/>
+      <c r="O422" s="15" t="n"/>
     </row>
     <row r="423">
       <c r="A423" s="3" t="inlineStr">
@@ -20940,9 +21362,10 @@
       </c>
       <c r="L423" s="7" t="n"/>
       <c r="M423" s="8" t="n"/>
-      <c r="N423" s="8" t="n"/>
-    </row>
-    <row r="424" ht="26.4" customHeight="1" s="17">
+      <c r="N423" s="17" t="n"/>
+      <c r="O423" s="15" t="n"/>
+    </row>
+    <row r="424" ht="26.4" customHeight="1" s="20">
       <c r="A424" s="3" t="inlineStr">
         <is>
           <t>Telit_DOCCENTER.DbLib</t>
@@ -20985,12 +21408,13 @@
           <t>MAT-4223</t>
         </is>
       </c>
-      <c r="N424" s="10" t="inlineStr">
+      <c r="N424" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">WALSIN	 - WR06X60R4FTL
 FENGHUA - RS-03K60R4FT　</t>
         </is>
       </c>
+      <c r="O424" s="15" t="n"/>
     </row>
     <row r="425">
       <c r="A425" s="3" t="inlineStr">
@@ -21032,7 +21456,8 @@
       </c>
       <c r="L425" s="7" t="n"/>
       <c r="M425" s="8" t="n"/>
-      <c r="N425" s="8" t="n"/>
+      <c r="N425" s="17" t="n"/>
+      <c r="O425" s="15" t="n"/>
     </row>
     <row r="426">
       <c r="A426" s="3" t="inlineStr">
@@ -21074,9 +21499,10 @@
       </c>
       <c r="L426" s="7" t="n"/>
       <c r="M426" s="8" t="n"/>
-      <c r="N426" s="8" t="n"/>
-    </row>
-    <row r="427" ht="26.4" customHeight="1" s="17">
+      <c r="N426" s="17" t="n"/>
+      <c r="O426" s="15" t="n"/>
+    </row>
+    <row r="427" ht="26.4" customHeight="1" s="20">
       <c r="A427" s="3" t="inlineStr">
         <is>
           <t>Telit_DOCCENTER.DbLib</t>
@@ -21119,14 +21545,15 @@
           <t>MAT-4223</t>
         </is>
       </c>
-      <c r="N427" s="10" t="inlineStr">
+      <c r="N427" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">WALSIN	 - WR06X60R4FTL
 FENGHUA - RS-03K60R4FT　</t>
         </is>
       </c>
-    </row>
-    <row r="428" ht="26.4" customHeight="1" s="17">
+      <c r="O427" s="15" t="n"/>
+    </row>
+    <row r="428" ht="26.4" customHeight="1" s="20">
       <c r="A428" s="3" t="inlineStr">
         <is>
           <t>Telit_DOCCENTER.DbLib</t>
@@ -21169,12 +21596,13 @@
           <t>MAT-4223</t>
         </is>
       </c>
-      <c r="N428" s="10" t="inlineStr">
+      <c r="N428" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">WALSIN	 - WR06X60R4FTL
 FENGHUA - RS-03K60R4FT　</t>
         </is>
       </c>
+      <c r="O428" s="15" t="n"/>
     </row>
     <row r="429">
       <c r="A429" s="3" t="inlineStr">
@@ -21216,7 +21644,8 @@
       </c>
       <c r="L429" s="7" t="n"/>
       <c r="M429" s="8" t="n"/>
-      <c r="N429" s="8" t="n"/>
+      <c r="N429" s="17" t="n"/>
+      <c r="O429" s="15" t="n"/>
     </row>
     <row r="430">
       <c r="A430" s="3" t="inlineStr">
@@ -21258,9 +21687,10 @@
       </c>
       <c r="L430" s="7" t="n"/>
       <c r="M430" s="8" t="n"/>
-      <c r="N430" s="8" t="n"/>
-    </row>
-    <row r="431" ht="26.4" customHeight="1" s="17">
+      <c r="N430" s="17" t="n"/>
+      <c r="O430" s="15" t="n"/>
+    </row>
+    <row r="431" ht="26.4" customHeight="1" s="20">
       <c r="A431" s="3" t="inlineStr">
         <is>
           <t>Telit_DOCCENTER.DbLib</t>
@@ -21303,12 +21733,13 @@
           <t>MAT-4223</t>
         </is>
       </c>
-      <c r="N431" s="10" t="inlineStr">
+      <c r="N431" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">WALSIN	 - WR06X60R4FTL
 FENGHUA - RS-03K60R4FT　</t>
         </is>
       </c>
+      <c r="O431" s="15" t="n"/>
     </row>
     <row r="432">
       <c r="A432" s="3" t="inlineStr">
@@ -21350,7 +21781,8 @@
       </c>
       <c r="L432" s="7" t="n"/>
       <c r="M432" s="8" t="n"/>
-      <c r="N432" s="8" t="n"/>
+      <c r="N432" s="17" t="n"/>
+      <c r="O432" s="15" t="n"/>
     </row>
     <row r="433">
       <c r="A433" s="3" t="inlineStr">
@@ -21392,7 +21824,8 @@
       </c>
       <c r="L433" s="7" t="n"/>
       <c r="M433" s="8" t="n"/>
-      <c r="N433" s="8" t="n"/>
+      <c r="N433" s="17" t="n"/>
+      <c r="O433" s="15" t="n"/>
     </row>
     <row r="434">
       <c r="A434" s="3" t="inlineStr">
@@ -21434,7 +21867,8 @@
       </c>
       <c r="L434" s="7" t="n"/>
       <c r="M434" s="8" t="n"/>
-      <c r="N434" s="8" t="n"/>
+      <c r="N434" s="17" t="n"/>
+      <c r="O434" s="15" t="n"/>
     </row>
     <row r="435">
       <c r="A435" s="3" t="inlineStr">
@@ -21476,7 +21910,8 @@
       </c>
       <c r="L435" s="7" t="n"/>
       <c r="M435" s="8" t="n"/>
-      <c r="N435" s="8" t="n"/>
+      <c r="N435" s="17" t="n"/>
+      <c r="O435" s="15" t="n"/>
     </row>
     <row r="436">
       <c r="A436" s="3" t="inlineStr">
@@ -21518,7 +21953,8 @@
       </c>
       <c r="L436" s="7" t="n"/>
       <c r="M436" s="8" t="n"/>
-      <c r="N436" s="8" t="n"/>
+      <c r="N436" s="17" t="n"/>
+      <c r="O436" s="15" t="n"/>
     </row>
     <row r="437">
       <c r="A437" s="3" t="inlineStr">
@@ -21560,7 +21996,8 @@
       </c>
       <c r="L437" s="7" t="n"/>
       <c r="M437" s="8" t="n"/>
-      <c r="N437" s="8" t="n"/>
+      <c r="N437" s="17" t="n"/>
+      <c r="O437" s="15" t="n"/>
     </row>
     <row r="438">
       <c r="A438" s="3" t="inlineStr">
@@ -21602,7 +22039,8 @@
       </c>
       <c r="L438" s="7" t="n"/>
       <c r="M438" s="8" t="n"/>
-      <c r="N438" s="8" t="n"/>
+      <c r="N438" s="17" t="n"/>
+      <c r="O438" s="15" t="n"/>
     </row>
     <row r="439">
       <c r="A439" s="3" t="inlineStr">
@@ -21644,7 +22082,8 @@
       </c>
       <c r="L439" s="7" t="n"/>
       <c r="M439" s="8" t="n"/>
-      <c r="N439" s="8" t="n"/>
+      <c r="N439" s="17" t="n"/>
+      <c r="O439" s="15" t="n"/>
     </row>
     <row r="440">
       <c r="A440" s="3" t="inlineStr">
@@ -21698,7 +22137,8 @@
       </c>
       <c r="L440" s="7" t="n"/>
       <c r="M440" s="8" t="n"/>
-      <c r="N440" s="8" t="n"/>
+      <c r="N440" s="17" t="n"/>
+      <c r="O440" s="15" t="n"/>
     </row>
     <row r="441">
       <c r="A441" s="3" t="inlineStr">
@@ -21740,7 +22180,8 @@
       </c>
       <c r="L441" s="7" t="n"/>
       <c r="M441" s="8" t="n"/>
-      <c r="N441" s="8" t="n"/>
+      <c r="N441" s="17" t="n"/>
+      <c r="O441" s="15" t="n"/>
     </row>
     <row r="442">
       <c r="A442" s="3" t="inlineStr">
@@ -21782,7 +22223,8 @@
       </c>
       <c r="L442" s="7" t="n"/>
       <c r="M442" s="8" t="n"/>
-      <c r="N442" s="8" t="n"/>
+      <c r="N442" s="17" t="n"/>
+      <c r="O442" s="15" t="n"/>
     </row>
     <row r="443">
       <c r="A443" s="3" t="inlineStr">
@@ -21824,7 +22266,8 @@
       </c>
       <c r="L443" s="7" t="n"/>
       <c r="M443" s="8" t="n"/>
-      <c r="N443" s="8" t="n"/>
+      <c r="N443" s="17" t="n"/>
+      <c r="O443" s="15" t="n"/>
     </row>
     <row r="444">
       <c r="A444" s="3" t="inlineStr">
@@ -21866,7 +22309,8 @@
       </c>
       <c r="L444" s="7" t="n"/>
       <c r="M444" s="8" t="n"/>
-      <c r="N444" s="8" t="n"/>
+      <c r="N444" s="17" t="n"/>
+      <c r="O444" s="15" t="n"/>
     </row>
     <row r="445">
       <c r="A445" s="3" t="inlineStr">
@@ -21908,7 +22352,8 @@
       </c>
       <c r="L445" s="7" t="n"/>
       <c r="M445" s="8" t="n"/>
-      <c r="N445" s="8" t="n"/>
+      <c r="N445" s="17" t="n"/>
+      <c r="O445" s="15" t="n"/>
     </row>
     <row r="446">
       <c r="A446" s="3" t="inlineStr">
@@ -21962,7 +22407,8 @@
       </c>
       <c r="L446" s="7" t="n"/>
       <c r="M446" s="8" t="n"/>
-      <c r="N446" s="8" t="n"/>
+      <c r="N446" s="17" t="n"/>
+      <c r="O446" s="15" t="n"/>
     </row>
     <row r="447">
       <c r="A447" s="3" t="inlineStr">
@@ -22004,7 +22450,8 @@
       </c>
       <c r="L447" s="7" t="n"/>
       <c r="M447" s="8" t="n"/>
-      <c r="N447" s="8" t="n"/>
+      <c r="N447" s="17" t="n"/>
+      <c r="O447" s="15" t="n"/>
     </row>
     <row r="448">
       <c r="A448" s="3" t="inlineStr">
@@ -22058,7 +22505,8 @@
       </c>
       <c r="L448" s="7" t="n"/>
       <c r="M448" s="8" t="n"/>
-      <c r="N448" s="8" t="n"/>
+      <c r="N448" s="17" t="n"/>
+      <c r="O448" s="15" t="n"/>
     </row>
     <row r="449">
       <c r="A449" s="3" t="inlineStr">
@@ -22112,7 +22560,8 @@
       </c>
       <c r="L449" s="7" t="n"/>
       <c r="M449" s="8" t="n"/>
-      <c r="N449" s="8" t="n"/>
+      <c r="N449" s="17" t="n"/>
+      <c r="O449" s="15" t="n"/>
     </row>
     <row r="450">
       <c r="A450" s="3" t="inlineStr">
@@ -22154,7 +22603,8 @@
       </c>
       <c r="L450" s="7" t="n"/>
       <c r="M450" s="8" t="n"/>
-      <c r="N450" s="8" t="n"/>
+      <c r="N450" s="17" t="n"/>
+      <c r="O450" s="15" t="n"/>
     </row>
     <row r="451">
       <c r="A451" s="3" t="inlineStr">
@@ -22208,7 +22658,8 @@
       </c>
       <c r="L451" s="7" t="n"/>
       <c r="M451" s="8" t="n"/>
-      <c r="N451" s="8" t="n"/>
+      <c r="N451" s="17" t="n"/>
+      <c r="O451" s="15" t="n"/>
     </row>
     <row r="452">
       <c r="A452" s="3" t="inlineStr">
@@ -22250,7 +22701,8 @@
       </c>
       <c r="L452" s="7" t="n"/>
       <c r="M452" s="8" t="n"/>
-      <c r="N452" s="8" t="n"/>
+      <c r="N452" s="17" t="n"/>
+      <c r="O452" s="15" t="n"/>
     </row>
     <row r="453">
       <c r="A453" s="3" t="inlineStr">
@@ -22304,7 +22756,8 @@
       </c>
       <c r="L453" s="7" t="n"/>
       <c r="M453" s="8" t="n"/>
-      <c r="N453" s="8" t="n"/>
+      <c r="N453" s="17" t="n"/>
+      <c r="O453" s="15" t="n"/>
     </row>
     <row r="454">
       <c r="A454" s="3" t="inlineStr">
@@ -22346,7 +22799,8 @@
       </c>
       <c r="L454" s="7" t="n"/>
       <c r="M454" s="8" t="n"/>
-      <c r="N454" s="8" t="n"/>
+      <c r="N454" s="17" t="n"/>
+      <c r="O454" s="15" t="n"/>
     </row>
     <row r="455">
       <c r="A455" s="3" t="inlineStr">
@@ -22388,7 +22842,8 @@
       </c>
       <c r="L455" s="7" t="n"/>
       <c r="M455" s="8" t="n"/>
-      <c r="N455" s="8" t="n"/>
+      <c r="N455" s="17" t="n"/>
+      <c r="O455" s="15" t="n"/>
     </row>
     <row r="456">
       <c r="A456" s="3" t="inlineStr">
@@ -22430,7 +22885,8 @@
       </c>
       <c r="L456" s="7" t="n"/>
       <c r="M456" s="8" t="n"/>
-      <c r="N456" s="8" t="n"/>
+      <c r="N456" s="17" t="n"/>
+      <c r="O456" s="15" t="n"/>
     </row>
     <row r="457">
       <c r="A457" s="3" t="inlineStr">
@@ -22484,7 +22940,8 @@
       </c>
       <c r="L457" s="7" t="n"/>
       <c r="M457" s="8" t="n"/>
-      <c r="N457" s="8" t="n"/>
+      <c r="N457" s="17" t="n"/>
+      <c r="O457" s="15" t="n"/>
     </row>
     <row r="458">
       <c r="A458" s="3" t="inlineStr">
@@ -22538,7 +22995,8 @@
       </c>
       <c r="L458" s="7" t="n"/>
       <c r="M458" s="8" t="n"/>
-      <c r="N458" s="8" t="n"/>
+      <c r="N458" s="17" t="n"/>
+      <c r="O458" s="15" t="n"/>
     </row>
     <row r="459">
       <c r="A459" s="3" t="inlineStr">
@@ -22580,7 +23038,8 @@
       </c>
       <c r="L459" s="7" t="n"/>
       <c r="M459" s="8" t="n"/>
-      <c r="N459" s="8" t="n"/>
+      <c r="N459" s="17" t="n"/>
+      <c r="O459" s="15" t="n"/>
     </row>
     <row r="460">
       <c r="A460" s="3" t="inlineStr">
@@ -22634,7 +23093,8 @@
       </c>
       <c r="L460" s="7" t="n"/>
       <c r="M460" s="8" t="n"/>
-      <c r="N460" s="8" t="n"/>
+      <c r="N460" s="17" t="n"/>
+      <c r="O460" s="15" t="n"/>
     </row>
     <row r="461">
       <c r="A461" s="3" t="inlineStr">
@@ -22676,7 +23136,8 @@
       </c>
       <c r="L461" s="7" t="n"/>
       <c r="M461" s="8" t="n"/>
-      <c r="N461" s="8" t="n"/>
+      <c r="N461" s="17" t="n"/>
+      <c r="O461" s="15" t="n"/>
     </row>
     <row r="462">
       <c r="A462" s="3" t="inlineStr">
@@ -22730,7 +23191,8 @@
       </c>
       <c r="L462" s="7" t="n"/>
       <c r="M462" s="8" t="n"/>
-      <c r="N462" s="8" t="n"/>
+      <c r="N462" s="17" t="n"/>
+      <c r="O462" s="15" t="n"/>
     </row>
     <row r="463">
       <c r="A463" s="3" t="inlineStr">
@@ -22784,7 +23246,8 @@
       </c>
       <c r="L463" s="7" t="n"/>
       <c r="M463" s="8" t="n"/>
-      <c r="N463" s="8" t="n"/>
+      <c r="N463" s="17" t="n"/>
+      <c r="O463" s="15" t="n"/>
     </row>
     <row r="464">
       <c r="A464" s="3" t="inlineStr">
@@ -22838,7 +23301,8 @@
       </c>
       <c r="L464" s="7" t="n"/>
       <c r="M464" s="8" t="n"/>
-      <c r="N464" s="8" t="n"/>
+      <c r="N464" s="17" t="n"/>
+      <c r="O464" s="15" t="n"/>
     </row>
     <row r="465">
       <c r="A465" s="3" t="inlineStr">
@@ -22880,7 +23344,8 @@
       </c>
       <c r="L465" s="7" t="n"/>
       <c r="M465" s="8" t="n"/>
-      <c r="N465" s="8" t="n"/>
+      <c r="N465" s="17" t="n"/>
+      <c r="O465" s="15" t="n"/>
     </row>
     <row r="466">
       <c r="A466" s="3" t="inlineStr">
@@ -22922,7 +23387,8 @@
       </c>
       <c r="L466" s="7" t="n"/>
       <c r="M466" s="8" t="n"/>
-      <c r="N466" s="8" t="n"/>
+      <c r="N466" s="17" t="n"/>
+      <c r="O466" s="15" t="n"/>
     </row>
     <row r="467">
       <c r="A467" s="3" t="inlineStr">
@@ -22964,7 +23430,8 @@
       </c>
       <c r="L467" s="7" t="n"/>
       <c r="M467" s="8" t="n"/>
-      <c r="N467" s="8" t="n"/>
+      <c r="N467" s="17" t="n"/>
+      <c r="O467" s="15" t="n"/>
     </row>
     <row r="468">
       <c r="A468" s="3" t="inlineStr">
@@ -23006,7 +23473,8 @@
       </c>
       <c r="L468" s="7" t="n"/>
       <c r="M468" s="8" t="n"/>
-      <c r="N468" s="8" t="n"/>
+      <c r="N468" s="17" t="n"/>
+      <c r="O468" s="15" t="n"/>
     </row>
     <row r="469">
       <c r="A469" s="3" t="inlineStr">
@@ -23048,7 +23516,8 @@
       </c>
       <c r="L469" s="7" t="n"/>
       <c r="M469" s="8" t="n"/>
-      <c r="N469" s="8" t="n"/>
+      <c r="N469" s="17" t="n"/>
+      <c r="O469" s="15" t="n"/>
     </row>
     <row r="470">
       <c r="A470" s="3" t="inlineStr">
@@ -23090,7 +23559,8 @@
       </c>
       <c r="L470" s="7" t="n"/>
       <c r="M470" s="8" t="n"/>
-      <c r="N470" s="8" t="n"/>
+      <c r="N470" s="17" t="n"/>
+      <c r="O470" s="15" t="n"/>
     </row>
     <row r="471">
       <c r="A471" s="3" t="inlineStr">
@@ -23132,7 +23602,8 @@
       </c>
       <c r="L471" s="7" t="n"/>
       <c r="M471" s="8" t="n"/>
-      <c r="N471" s="8" t="n"/>
+      <c r="N471" s="17" t="n"/>
+      <c r="O471" s="15" t="n"/>
     </row>
     <row r="472">
       <c r="A472" s="3" t="inlineStr">
@@ -23174,7 +23645,8 @@
       </c>
       <c r="L472" s="7" t="n"/>
       <c r="M472" s="8" t="n"/>
-      <c r="N472" s="8" t="n"/>
+      <c r="N472" s="17" t="n"/>
+      <c r="O472" s="15" t="n"/>
     </row>
     <row r="473">
       <c r="A473" s="3" t="inlineStr">
@@ -23216,7 +23688,8 @@
       </c>
       <c r="L473" s="7" t="n"/>
       <c r="M473" s="8" t="n"/>
-      <c r="N473" s="8" t="n"/>
+      <c r="N473" s="17" t="n"/>
+      <c r="O473" s="15" t="n"/>
     </row>
     <row r="474">
       <c r="A474" s="3" t="inlineStr">
@@ -23258,7 +23731,8 @@
       </c>
       <c r="L474" s="7" t="n"/>
       <c r="M474" s="8" t="n"/>
-      <c r="N474" s="8" t="n"/>
+      <c r="N474" s="17" t="n"/>
+      <c r="O474" s="15" t="n"/>
     </row>
     <row r="475">
       <c r="A475" s="3" t="inlineStr">
@@ -23300,7 +23774,8 @@
       </c>
       <c r="L475" s="7" t="n"/>
       <c r="M475" s="8" t="n"/>
-      <c r="N475" s="8" t="n"/>
+      <c r="N475" s="17" t="n"/>
+      <c r="O475" s="15" t="n"/>
     </row>
     <row r="476">
       <c r="A476" s="3" t="inlineStr">
@@ -23342,7 +23817,8 @@
       </c>
       <c r="L476" s="7" t="n"/>
       <c r="M476" s="8" t="n"/>
-      <c r="N476" s="8" t="n"/>
+      <c r="N476" s="17" t="n"/>
+      <c r="O476" s="15" t="n"/>
     </row>
     <row r="477">
       <c r="A477" s="3" t="inlineStr">
@@ -23384,7 +23860,8 @@
       </c>
       <c r="L477" s="7" t="n"/>
       <c r="M477" s="8" t="n"/>
-      <c r="N477" s="8" t="n"/>
+      <c r="N477" s="17" t="n"/>
+      <c r="O477" s="15" t="n"/>
     </row>
     <row r="478">
       <c r="A478" s="3" t="inlineStr">
@@ -23426,7 +23903,8 @@
       </c>
       <c r="L478" s="7" t="n"/>
       <c r="M478" s="8" t="n"/>
-      <c r="N478" s="8" t="n"/>
+      <c r="N478" s="17" t="n"/>
+      <c r="O478" s="15" t="n"/>
     </row>
     <row r="479">
       <c r="A479" s="3" t="inlineStr">
@@ -23468,7 +23946,8 @@
       </c>
       <c r="L479" s="7" t="n"/>
       <c r="M479" s="8" t="n"/>
-      <c r="N479" s="8" t="n"/>
+      <c r="N479" s="17" t="n"/>
+      <c r="O479" s="15" t="n"/>
     </row>
     <row r="480">
       <c r="A480" s="3" t="inlineStr">
@@ -23510,7 +23989,8 @@
       </c>
       <c r="L480" s="7" t="n"/>
       <c r="M480" s="8" t="n"/>
-      <c r="N480" s="8" t="n"/>
+      <c r="N480" s="17" t="n"/>
+      <c r="O480" s="15" t="n"/>
     </row>
     <row r="481">
       <c r="A481" s="3" t="inlineStr">
@@ -23564,7 +24044,8 @@
       </c>
       <c r="L481" s="7" t="n"/>
       <c r="M481" s="8" t="n"/>
-      <c r="N481" s="8" t="n"/>
+      <c r="N481" s="17" t="n"/>
+      <c r="O481" s="15" t="n"/>
     </row>
     <row r="482">
       <c r="A482" s="3" t="inlineStr">
@@ -23606,7 +24087,8 @@
       </c>
       <c r="L482" s="7" t="n"/>
       <c r="M482" s="8" t="n"/>
-      <c r="N482" s="8" t="n"/>
+      <c r="N482" s="17" t="n"/>
+      <c r="O482" s="15" t="n"/>
     </row>
     <row r="483">
       <c r="A483" s="3" t="inlineStr">
@@ -23648,7 +24130,8 @@
       </c>
       <c r="L483" s="7" t="n"/>
       <c r="M483" s="8" t="n"/>
-      <c r="N483" s="8" t="n"/>
+      <c r="N483" s="17" t="n"/>
+      <c r="O483" s="15" t="n"/>
     </row>
     <row r="484">
       <c r="A484" s="3" t="inlineStr">
@@ -23690,7 +24173,8 @@
       </c>
       <c r="L484" s="7" t="n"/>
       <c r="M484" s="8" t="n"/>
-      <c r="N484" s="8" t="n"/>
+      <c r="N484" s="17" t="n"/>
+      <c r="O484" s="15" t="n"/>
     </row>
     <row r="485">
       <c r="A485" s="3" t="inlineStr">
@@ -23744,7 +24228,8 @@
       </c>
       <c r="L485" s="7" t="n"/>
       <c r="M485" s="8" t="n"/>
-      <c r="N485" s="8" t="n"/>
+      <c r="N485" s="17" t="n"/>
+      <c r="O485" s="15" t="n"/>
     </row>
     <row r="486">
       <c r="A486" s="3" t="inlineStr">
@@ -23786,7 +24271,8 @@
       </c>
       <c r="L486" s="7" t="n"/>
       <c r="M486" s="8" t="n"/>
-      <c r="N486" s="8" t="n"/>
+      <c r="N486" s="17" t="n"/>
+      <c r="O486" s="15" t="n"/>
     </row>
     <row r="487">
       <c r="A487" s="3" t="inlineStr">
@@ -23828,7 +24314,8 @@
       </c>
       <c r="L487" s="7" t="n"/>
       <c r="M487" s="8" t="n"/>
-      <c r="N487" s="8" t="n"/>
+      <c r="N487" s="17" t="n"/>
+      <c r="O487" s="15" t="n"/>
     </row>
     <row r="488">
       <c r="A488" s="3" t="inlineStr">
@@ -23882,7 +24369,8 @@
       </c>
       <c r="L488" s="7" t="n"/>
       <c r="M488" s="8" t="n"/>
-      <c r="N488" s="8" t="n"/>
+      <c r="N488" s="17" t="n"/>
+      <c r="O488" s="15" t="n"/>
     </row>
     <row r="489">
       <c r="A489" s="3" t="inlineStr">
@@ -23936,7 +24424,8 @@
       </c>
       <c r="L489" s="7" t="n"/>
       <c r="M489" s="8" t="n"/>
-      <c r="N489" s="8" t="n"/>
+      <c r="N489" s="17" t="n"/>
+      <c r="O489" s="15" t="n"/>
     </row>
     <row r="490">
       <c r="A490" s="3" t="inlineStr">
@@ -23986,7 +24475,8 @@
       </c>
       <c r="L490" s="7" t="n"/>
       <c r="M490" s="8" t="n"/>
-      <c r="N490" s="8" t="n"/>
+      <c r="N490" s="17" t="n"/>
+      <c r="O490" s="15" t="n"/>
     </row>
     <row r="491">
       <c r="A491" s="3" t="inlineStr">
@@ -24040,7 +24530,8 @@
       </c>
       <c r="L491" s="7" t="n"/>
       <c r="M491" s="8" t="n"/>
-      <c r="N491" s="8" t="n"/>
+      <c r="N491" s="17" t="n"/>
+      <c r="O491" s="15" t="n"/>
     </row>
     <row r="492">
       <c r="A492" s="3" t="inlineStr">
@@ -24094,7 +24585,8 @@
       </c>
       <c r="L492" s="7" t="n"/>
       <c r="M492" s="8" t="n"/>
-      <c r="N492" s="8" t="n"/>
+      <c r="N492" s="17" t="n"/>
+      <c r="O492" s="15" t="n"/>
     </row>
     <row r="493">
       <c r="A493" s="3" t="inlineStr">
@@ -24148,7 +24640,8 @@
       </c>
       <c r="L493" s="7" t="n"/>
       <c r="M493" s="8" t="n"/>
-      <c r="N493" s="8" t="n"/>
+      <c r="N493" s="17" t="n"/>
+      <c r="O493" s="15" t="n"/>
     </row>
     <row r="494">
       <c r="A494" s="3" t="inlineStr">
@@ -24202,7 +24695,8 @@
       </c>
       <c r="L494" s="7" t="n"/>
       <c r="M494" s="8" t="n"/>
-      <c r="N494" s="8" t="n"/>
+      <c r="N494" s="17" t="n"/>
+      <c r="O494" s="15" t="n"/>
     </row>
     <row r="495">
       <c r="A495" s="3" t="inlineStr">
@@ -24256,7 +24750,8 @@
       </c>
       <c r="L495" s="7" t="n"/>
       <c r="M495" s="8" t="n"/>
-      <c r="N495" s="8" t="n"/>
+      <c r="N495" s="17" t="n"/>
+      <c r="O495" s="15" t="n"/>
     </row>
     <row r="496">
       <c r="A496" s="3" t="inlineStr">
@@ -24310,7 +24805,8 @@
       </c>
       <c r="L496" s="7" t="n"/>
       <c r="M496" s="8" t="n"/>
-      <c r="N496" s="8" t="n"/>
+      <c r="N496" s="17" t="n"/>
+      <c r="O496" s="15" t="n"/>
     </row>
     <row r="497">
       <c r="A497" s="3" t="inlineStr">
@@ -24364,7 +24860,8 @@
       </c>
       <c r="L497" s="7" t="n"/>
       <c r="M497" s="8" t="n"/>
-      <c r="N497" s="8" t="n"/>
+      <c r="N497" s="17" t="n"/>
+      <c r="O497" s="15" t="n"/>
     </row>
     <row r="498">
       <c r="A498" s="3" t="inlineStr">
@@ -24418,7 +24915,8 @@
       </c>
       <c r="L498" s="7" t="n"/>
       <c r="M498" s="8" t="n"/>
-      <c r="N498" s="8" t="n"/>
+      <c r="N498" s="17" t="n"/>
+      <c r="O498" s="15" t="n"/>
     </row>
     <row r="499">
       <c r="A499" s="3" t="inlineStr">
@@ -24472,7 +24970,8 @@
       </c>
       <c r="L499" s="7" t="n"/>
       <c r="M499" s="8" t="n"/>
-      <c r="N499" s="8" t="n"/>
+      <c r="N499" s="17" t="n"/>
+      <c r="O499" s="15" t="n"/>
     </row>
     <row r="500">
       <c r="A500" s="3" t="inlineStr">
@@ -24526,7 +25025,8 @@
       </c>
       <c r="L500" s="7" t="n"/>
       <c r="M500" s="8" t="n"/>
-      <c r="N500" s="8" t="n"/>
+      <c r="N500" s="17" t="n"/>
+      <c r="O500" s="15" t="n"/>
     </row>
     <row r="501">
       <c r="A501" s="3" t="inlineStr">
@@ -24580,7 +25080,8 @@
       </c>
       <c r="L501" s="7" t="n"/>
       <c r="M501" s="8" t="n"/>
-      <c r="N501" s="8" t="n"/>
+      <c r="N501" s="17" t="n"/>
+      <c r="O501" s="15" t="n"/>
     </row>
     <row r="502">
       <c r="A502" s="3" t="inlineStr">
@@ -24634,7 +25135,8 @@
       </c>
       <c r="L502" s="7" t="n"/>
       <c r="M502" s="8" t="n"/>
-      <c r="N502" s="8" t="n"/>
+      <c r="N502" s="17" t="n"/>
+      <c r="O502" s="15" t="n"/>
     </row>
     <row r="503">
       <c r="A503" s="3" t="inlineStr">
@@ -24688,7 +25190,8 @@
       </c>
       <c r="L503" s="7" t="n"/>
       <c r="M503" s="8" t="n"/>
-      <c r="N503" s="8" t="n"/>
+      <c r="N503" s="17" t="n"/>
+      <c r="O503" s="15" t="n"/>
     </row>
     <row r="504">
       <c r="A504" s="3" t="inlineStr">
@@ -24742,7 +25245,8 @@
       </c>
       <c r="L504" s="7" t="n"/>
       <c r="M504" s="8" t="n"/>
-      <c r="N504" s="8" t="n"/>
+      <c r="N504" s="17" t="n"/>
+      <c r="O504" s="15" t="n"/>
     </row>
     <row r="505">
       <c r="A505" s="3" t="inlineStr">
@@ -24796,7 +25300,8 @@
       </c>
       <c r="L505" s="7" t="n"/>
       <c r="M505" s="8" t="n"/>
-      <c r="N505" s="8" t="n"/>
+      <c r="N505" s="17" t="n"/>
+      <c r="O505" s="15" t="n"/>
     </row>
     <row r="506">
       <c r="A506" s="3" t="inlineStr">
@@ -24850,7 +25355,8 @@
       </c>
       <c r="L506" s="7" t="n"/>
       <c r="M506" s="8" t="n"/>
-      <c r="N506" s="8" t="n"/>
+      <c r="N506" s="17" t="n"/>
+      <c r="O506" s="15" t="n"/>
     </row>
     <row r="507">
       <c r="A507" s="3" t="inlineStr">
@@ -24904,7 +25410,8 @@
       </c>
       <c r="L507" s="7" t="n"/>
       <c r="M507" s="8" t="n"/>
-      <c r="N507" s="8" t="n"/>
+      <c r="N507" s="17" t="n"/>
+      <c r="O507" s="15" t="n"/>
     </row>
     <row r="508">
       <c r="A508" s="3" t="inlineStr">
@@ -24958,7 +25465,8 @@
       </c>
       <c r="L508" s="7" t="n"/>
       <c r="M508" s="8" t="n"/>
-      <c r="N508" s="8" t="n"/>
+      <c r="N508" s="17" t="n"/>
+      <c r="O508" s="15" t="n"/>
     </row>
     <row r="509">
       <c r="A509" s="3" t="inlineStr">
@@ -25012,7 +25520,8 @@
       </c>
       <c r="L509" s="7" t="n"/>
       <c r="M509" s="8" t="n"/>
-      <c r="N509" s="8" t="n"/>
+      <c r="N509" s="17" t="n"/>
+      <c r="O509" s="15" t="n"/>
     </row>
     <row r="510">
       <c r="A510" s="3" t="inlineStr">
@@ -25066,7 +25575,8 @@
       </c>
       <c r="L510" s="7" t="n"/>
       <c r="M510" s="8" t="n"/>
-      <c r="N510" s="8" t="n"/>
+      <c r="N510" s="17" t="n"/>
+      <c r="O510" s="15" t="n"/>
     </row>
     <row r="511">
       <c r="A511" s="3" t="inlineStr">
@@ -25120,7 +25630,8 @@
       </c>
       <c r="L511" s="7" t="n"/>
       <c r="M511" s="8" t="n"/>
-      <c r="N511" s="8" t="n"/>
+      <c r="N511" s="17" t="n"/>
+      <c r="O511" s="15" t="n"/>
     </row>
     <row r="512">
       <c r="A512" s="3" t="inlineStr">
@@ -25174,7 +25685,8 @@
       </c>
       <c r="L512" s="7" t="n"/>
       <c r="M512" s="8" t="n"/>
-      <c r="N512" s="8" t="n"/>
+      <c r="N512" s="17" t="n"/>
+      <c r="O512" s="15" t="n"/>
     </row>
     <row r="513">
       <c r="A513" s="3" t="inlineStr">
@@ -25228,7 +25740,8 @@
       </c>
       <c r="L513" s="7" t="n"/>
       <c r="M513" s="8" t="n"/>
-      <c r="N513" s="8" t="n"/>
+      <c r="N513" s="17" t="n"/>
+      <c r="O513" s="15" t="n"/>
     </row>
     <row r="514">
       <c r="A514" s="3" t="inlineStr">
@@ -25285,12 +25798,13 @@
           <t>EOL</t>
         </is>
       </c>
-      <c r="M514" s="12" t="inlineStr">
+      <c r="M514" s="10" t="inlineStr">
         <is>
           <t>REMOVED FROM PROJECT</t>
         </is>
       </c>
-      <c r="N514" s="8" t="n"/>
+      <c r="N514" s="17" t="n"/>
+      <c r="O514" s="15" t="n"/>
     </row>
     <row r="515">
       <c r="A515" s="3" t="inlineStr">
@@ -25344,7 +25858,8 @@
       </c>
       <c r="L515" s="7" t="n"/>
       <c r="M515" s="8" t="n"/>
-      <c r="N515" s="8" t="n"/>
+      <c r="N515" s="17" t="n"/>
+      <c r="O515" s="15" t="n"/>
     </row>
     <row r="516">
       <c r="A516" s="3" t="inlineStr">
@@ -25398,7 +25913,8 @@
       </c>
       <c r="L516" s="7" t="n"/>
       <c r="M516" s="8" t="n"/>
-      <c r="N516" s="8" t="n"/>
+      <c r="N516" s="17" t="n"/>
+      <c r="O516" s="15" t="n"/>
     </row>
     <row r="517">
       <c r="A517" s="3" t="inlineStr">
@@ -25452,7 +25968,8 @@
       </c>
       <c r="L517" s="7" t="n"/>
       <c r="M517" s="8" t="n"/>
-      <c r="N517" s="8" t="n"/>
+      <c r="N517" s="17" t="n"/>
+      <c r="O517" s="15" t="n"/>
     </row>
     <row r="518">
       <c r="A518" s="3" t="inlineStr">
@@ -25506,7 +26023,8 @@
       </c>
       <c r="L518" s="7" t="n"/>
       <c r="M518" s="8" t="n"/>
-      <c r="N518" s="8" t="n"/>
+      <c r="N518" s="17" t="n"/>
+      <c r="O518" s="15" t="n"/>
     </row>
     <row r="519">
       <c r="A519" s="3" t="inlineStr">
@@ -25560,7 +26078,8 @@
       </c>
       <c r="L519" s="7" t="n"/>
       <c r="M519" s="8" t="n"/>
-      <c r="N519" s="8" t="n"/>
+      <c r="N519" s="17" t="n"/>
+      <c r="O519" s="15" t="n"/>
     </row>
     <row r="520">
       <c r="A520" s="3" t="inlineStr">
@@ -25614,7 +26133,8 @@
       </c>
       <c r="L520" s="7" t="n"/>
       <c r="M520" s="8" t="n"/>
-      <c r="N520" s="8" t="n"/>
+      <c r="N520" s="17" t="n"/>
+      <c r="O520" s="15" t="n"/>
     </row>
     <row r="521">
       <c r="A521" s="3" t="inlineStr">
@@ -25668,7 +26188,8 @@
       </c>
       <c r="L521" s="7" t="n"/>
       <c r="M521" s="8" t="n"/>
-      <c r="N521" s="8" t="n"/>
+      <c r="N521" s="17" t="n"/>
+      <c r="O521" s="15" t="n"/>
     </row>
     <row r="522">
       <c r="A522" s="3" t="inlineStr">
@@ -25710,7 +26231,8 @@
       </c>
       <c r="L522" s="7" t="n"/>
       <c r="M522" s="8" t="n"/>
-      <c r="N522" s="8" t="n"/>
+      <c r="N522" s="17" t="n"/>
+      <c r="O522" s="15" t="n"/>
     </row>
     <row r="523">
       <c r="A523" s="3" t="inlineStr">
@@ -25764,7 +26286,8 @@
       </c>
       <c r="L523" s="7" t="n"/>
       <c r="M523" s="8" t="n"/>
-      <c r="N523" s="8" t="n"/>
+      <c r="N523" s="17" t="n"/>
+      <c r="O523" s="15" t="n"/>
     </row>
     <row r="524">
       <c r="A524" s="3" t="inlineStr">
@@ -25806,7 +26329,8 @@
       </c>
       <c r="L524" s="7" t="n"/>
       <c r="M524" s="8" t="n"/>
-      <c r="N524" s="8" t="n"/>
+      <c r="N524" s="17" t="n"/>
+      <c r="O524" s="15" t="n"/>
     </row>
     <row r="525">
       <c r="A525" s="3" t="inlineStr">
@@ -25848,7 +26372,8 @@
       </c>
       <c r="L525" s="7" t="n"/>
       <c r="M525" s="8" t="n"/>
-      <c r="N525" s="8" t="n"/>
+      <c r="N525" s="17" t="n"/>
+      <c r="O525" s="15" t="n"/>
     </row>
     <row r="526">
       <c r="A526" s="3" t="inlineStr">
@@ -25890,7 +26415,8 @@
       </c>
       <c r="L526" s="7" t="n"/>
       <c r="M526" s="8" t="n"/>
-      <c r="N526" s="8" t="n"/>
+      <c r="N526" s="17" t="n"/>
+      <c r="O526" s="15" t="n"/>
     </row>
     <row r="527">
       <c r="A527" s="3" t="inlineStr">
@@ -25932,7 +26458,8 @@
       </c>
       <c r="L527" s="7" t="n"/>
       <c r="M527" s="8" t="n"/>
-      <c r="N527" s="8" t="n"/>
+      <c r="N527" s="17" t="n"/>
+      <c r="O527" s="15" t="n"/>
     </row>
     <row r="528">
       <c r="A528" s="3" t="inlineStr">
@@ -25974,7 +26501,8 @@
       </c>
       <c r="L528" s="7" t="n"/>
       <c r="M528" s="8" t="n"/>
-      <c r="N528" s="8" t="n"/>
+      <c r="N528" s="17" t="n"/>
+      <c r="O528" s="15" t="n"/>
     </row>
     <row r="529">
       <c r="A529" s="3" t="inlineStr">
@@ -26016,7 +26544,8 @@
       </c>
       <c r="L529" s="7" t="n"/>
       <c r="M529" s="8" t="n"/>
-      <c r="N529" s="8" t="n"/>
+      <c r="N529" s="17" t="n"/>
+      <c r="O529" s="15" t="n"/>
     </row>
     <row r="530">
       <c r="A530" s="3" t="inlineStr">
@@ -26058,7 +26587,8 @@
       </c>
       <c r="L530" s="7" t="n"/>
       <c r="M530" s="8" t="n"/>
-      <c r="N530" s="8" t="n"/>
+      <c r="N530" s="17" t="n"/>
+      <c r="O530" s="15" t="n"/>
     </row>
     <row r="531">
       <c r="A531" s="3" t="inlineStr">
@@ -26100,7 +26630,8 @@
       </c>
       <c r="L531" s="7" t="n"/>
       <c r="M531" s="8" t="n"/>
-      <c r="N531" s="8" t="n"/>
+      <c r="N531" s="17" t="n"/>
+      <c r="O531" s="15" t="n"/>
     </row>
     <row r="532">
       <c r="A532" s="3" t="inlineStr">
@@ -26154,7 +26685,8 @@
       </c>
       <c r="L532" s="7" t="n"/>
       <c r="M532" s="8" t="n"/>
-      <c r="N532" s="8" t="n"/>
+      <c r="N532" s="17" t="n"/>
+      <c r="O532" s="15" t="n"/>
     </row>
     <row r="533">
       <c r="A533" s="3" t="inlineStr">
@@ -26208,7 +26740,8 @@
       </c>
       <c r="L533" s="7" t="n"/>
       <c r="M533" s="8" t="n"/>
-      <c r="N533" s="8" t="n"/>
+      <c r="N533" s="17" t="n"/>
+      <c r="O533" s="15" t="n"/>
     </row>
     <row r="534">
       <c r="A534" s="3" t="inlineStr">
@@ -26262,7 +26795,8 @@
       </c>
       <c r="L534" s="7" t="n"/>
       <c r="M534" s="8" t="n"/>
-      <c r="N534" s="8" t="n"/>
+      <c r="N534" s="17" t="n"/>
+      <c r="O534" s="15" t="n"/>
     </row>
     <row r="535">
       <c r="A535" s="3" t="inlineStr">
@@ -26316,7 +26850,8 @@
       </c>
       <c r="L535" s="7" t="n"/>
       <c r="M535" s="8" t="n"/>
-      <c r="N535" s="8" t="n"/>
+      <c r="N535" s="17" t="n"/>
+      <c r="O535" s="15" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -26325,16 +26860,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M171" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M230" display="https://pmo.telit.com/browse/MAT-4201" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M243" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M286" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M300" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M346" display="https://pmo.telit.com/browse/MAT-4224" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M356" display="https://pmo.telit.com/browse/MAT-4222" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M402" display="https://pmo.telit.com/browse/MAT-4220" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M404" display="https://pmo.telit.com/browse/MAT-4221" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M424" display="https://pmo.telit.com/browse/MAT-4223" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M427" display="https://pmo.telit.com/browse/MAT-4223" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M428" display="https://pmo.telit.com/browse/MAT-4223" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M431" display="https://pmo.telit.com/browse/MAT-4223" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M346" display="https://pmo.telit.com/browse/MAT-4224" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M356" display="https://pmo.telit.com/browse/MAT-4222" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M402" display="https://pmo.telit.com/browse/MAT-4220" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M404" display="https://pmo.telit.com/browse/MAT-4221" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M424" display="https://pmo.telit.com/browse/MAT-4223" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M427" display="https://pmo.telit.com/browse/MAT-4223" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M428" display="https://pmo.telit.com/browse/MAT-4223" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M431" display="https://pmo.telit.com/browse/MAT-4223" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>
